--- a/summaries/summary_report.xlsx
+++ b/summaries/summary_report.xlsx
@@ -1,114 +1,531 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="4"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Baseline vs Finetuned" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Baseline vs Finetuned" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="116">
+  <si>
+    <t xml:space="preserve">LM Playschool - Baseline vs Finetuned Results</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base models show absolute values. Finetuned models show the difference to their base model (finetuned - base):  green = improvement (+),  red = decline (-). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">playpen_clemscore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">playpen_statscore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_-, clemscore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_all, Average %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_all, Average QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OOD_-, clemscore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OOD_all, Average %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OOD_all, Average QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_adventuregame, %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_adventuregame, QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_bbh, %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_bbh, QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_cladder, %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_cladder, QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_clean_up, %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_clean_up, QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_codenames, %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_codenames, QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_dond, %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_dond, QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_eqbench, %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_eqbench, QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_guesswhat, %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_guesswhat, QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_ifeval, %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_ifeval, QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_imagegame, %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_imagegame, QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_matchit_ascii, %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_matchit_ascii, QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_mmlu_pro, %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_mmlu_pro, QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_privateshared, %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_privateshared, QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_referencegame, %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_referencegame, QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_taboo, %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_taboo, QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_textmapworld, %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_textmapworld, QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_textmapworld_graphreasoning, %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_textmapworld_graphreasoning, QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_textmapworld_specificroom, %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_textmapworld_specificroom, QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_wordle, %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_wordle, QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_wordle_withclue, %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_wordle_withclue, QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_wordle_withcritic, %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_wordle_withcritic, QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OOD_chronicle, %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OOD_chronicle, QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OOD_clockwork_courier, %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OOD_clockwork_courier, QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OOD_cryptolect, %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OOD_cryptolect, QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OOD_get_to_the_point, %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OOD_get_to_the_point, QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OOD_st_clean_up, %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OOD_st_clean_up, QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OOD_ta_blackjack, %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OOD_ta_blackjack, QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OOD_ta_frozen_lake, %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OOD_ta_frozen_lake, QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OOD_ta_mastermind, %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OOD_ta_mastermind, QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OOD_ta_sokoban, %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OOD_ta_sokoban, QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OOD_toh_multi_turn, %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OOD_toh_multi_turn, QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OOD_wordle-crazy, %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OOD_wordle-crazy, QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OOD_wordle-crazy_withclue, %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OOD_wordle-crazy_withclue, QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OOD_wordle-crazy_withcritic, %P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OOD_wordle-crazy_withcritic, QS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qwen3.5-2b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CityUoL__qwen3.5-2b__Qwen-GuidePlay-2B-v1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CityUoL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qwen-GuidePlay-2B-v1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAIR__qwen3.5-2b__sft-dpo-v2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAIR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sft-dpo-v2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAIR__qwen3.5-2b__sft-v1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sft-v1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">playornotplay__qwen3.5-2b__playornotplay-v1.0-merged-fp32-828e356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">playornotplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">playornotplay-v1.0-merged-fp32-7263076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qwen3.5-4b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bentel rockers__qwen3.5-4b__Bentel_iter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bentel rockers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bentel_iter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bentel rockers__qwen3.5-4b__Bentel_iter_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bentel_iter_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bentel rockers__qwen3.5-4b__Bentel_iter_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bentel_iter_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">llama-3.1-8b-instruct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qwen3.5-9b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSU-SLIM__Qwen3.5-9B-Base__playpen-prm-9b-best_of_n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BSU-SLIM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prm-search-best_of_n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialogue Architects__qwen3.5-9b__SCoRe_Qwen3.5-9B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialogue Architects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCoRe_Qwen3.5-9B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLP: Large Language Problems__qwen3.5-9b__llp-final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LLP: Large Language Problems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">llp-final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qwen3.5-27b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLED-BSU__Qwen3.5-27B-sft-ep1__prm-ep1-best_of_n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLED-BSU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prm-guided-best_of_n</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="\+0.00;\-0.00;0.00"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0.00"/>
+    <numFmt numFmtId="166" formatCode="\+0.00;\-0.00;0.00"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="16">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="14"/>
+      <family val="0"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
-      <i val="1"/>
-      <color theme="1"/>
-      <sz val="10"/>
+      <family val="0"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
+      <family val="0"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="10"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <color theme="1"/>
-      <sz val="10"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <b val="true"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="FF0000FF"/>
-      <sz val="10"/>
-      <u val="single"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="FF008000"/>
-      <sz val="10"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="FFC00000"/>
-      <sz val="10"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
+      <i val="true"/>
+      <u val="single"/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF008000"/>
       <name val="Calibri"/>
-      <color rgb="FF000000"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F3864"/>
-        <bgColor rgb="FF1F3864"/>
+        <bgColor rgb="FF333333"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
-        <bgColor rgb="FFD9E1F2"/>
+        <bgColor rgb="FFCCFFFF"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="2">
-    <border/>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
         <color rgb="FFBFBFBF"/>
       </left>
@@ -121,131 +538,166 @@
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
+  <cellXfs count="16">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="166" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
   <colors>
     <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFC00000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFBFBFBF"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFD9E1F2"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF1F3864"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -294,59 +746,55 @@
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Calibri" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Calibri" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -354,33 +802,24 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -393,13 +832,7 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -409,15 +842,13 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -425,7 +856,6 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -433,11 +863,11 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -446,441 +876,294 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:CA20"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:CA1000"/>
+  <sheetFormatPr defaultColWidth="14.43359375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col width="42" customWidth="1" style="15" min="1" max="1"/>
-    <col width="22" customWidth="1" style="15" min="2" max="3"/>
-    <col width="13" customWidth="1" style="15" min="4" max="79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="79" min="4" style="0" width="13"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>LM Playschool - Baseline vs Finetuned Results</t>
-        </is>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Base models show absolute values. Finetuned models show the difference to their base model (finetuned - base):  green = improvement (+),  red = decline (-).  Blank = value undefined for the base or the finetuned model.</t>
-        </is>
-      </c>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
     </row>
-    <row r="3"/>
-    <row r="4" ht="60" customHeight="1" s="15">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>team</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>version</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>playpen_clemscore</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>playpen_statscore</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>ID_-, clemscore</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>ID_all, Average %P</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>ID_all, Average QS</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>OOD_-, clemscore</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>OOD_all, Average %P</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>OOD_all, Average QS</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>ID_adventuregame, %P</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>ID_adventuregame, QS</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>ID_bbh, %P</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>ID_bbh, QS</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>ID_cladder, %P</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>ID_cladder, QS</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>ID_clean_up, %P</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>ID_clean_up, QS</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>ID_codenames, %P</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>ID_codenames, QS</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>ID_dond, %P</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t>ID_dond, QS</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>ID_eqbench, %P</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>ID_eqbench, QS</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>ID_guesswhat, %P</t>
-        </is>
-      </c>
-      <c r="AA4" s="3" t="inlineStr">
-        <is>
-          <t>ID_guesswhat, QS</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="inlineStr">
-        <is>
-          <t>ID_ifeval, %P</t>
-        </is>
-      </c>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>ID_ifeval, QS</t>
-        </is>
-      </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>ID_imagegame, %P</t>
-        </is>
-      </c>
-      <c r="AE4" s="3" t="inlineStr">
-        <is>
-          <t>ID_imagegame, QS</t>
-        </is>
-      </c>
-      <c r="AF4" s="3" t="inlineStr">
-        <is>
-          <t>ID_matchit_ascii, %P</t>
-        </is>
-      </c>
-      <c r="AG4" s="3" t="inlineStr">
-        <is>
-          <t>ID_matchit_ascii, QS</t>
-        </is>
-      </c>
-      <c r="AH4" s="3" t="inlineStr">
-        <is>
-          <t>ID_mmlu_pro, %P</t>
-        </is>
-      </c>
-      <c r="AI4" s="3" t="inlineStr">
-        <is>
-          <t>ID_mmlu_pro, QS</t>
-        </is>
-      </c>
-      <c r="AJ4" s="3" t="inlineStr">
-        <is>
-          <t>ID_privateshared, %P</t>
-        </is>
-      </c>
-      <c r="AK4" s="3" t="inlineStr">
-        <is>
-          <t>ID_privateshared, QS</t>
-        </is>
-      </c>
-      <c r="AL4" s="3" t="inlineStr">
-        <is>
-          <t>ID_referencegame, %P</t>
-        </is>
-      </c>
-      <c r="AM4" s="3" t="inlineStr">
-        <is>
-          <t>ID_referencegame, QS</t>
-        </is>
-      </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>ID_taboo, %P</t>
-        </is>
-      </c>
-      <c r="AO4" s="3" t="inlineStr">
-        <is>
-          <t>ID_taboo, QS</t>
-        </is>
-      </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>ID_textmapworld, %P</t>
-        </is>
-      </c>
-      <c r="AQ4" s="3" t="inlineStr">
-        <is>
-          <t>ID_textmapworld, QS</t>
-        </is>
-      </c>
-      <c r="AR4" s="3" t="inlineStr">
-        <is>
-          <t>ID_textmapworld_graphreasoning, %P</t>
-        </is>
-      </c>
-      <c r="AS4" s="3" t="inlineStr">
-        <is>
-          <t>ID_textmapworld_graphreasoning, QS</t>
-        </is>
-      </c>
-      <c r="AT4" s="3" t="inlineStr">
-        <is>
-          <t>ID_textmapworld_specificroom, %P</t>
-        </is>
-      </c>
-      <c r="AU4" s="3" t="inlineStr">
-        <is>
-          <t>ID_textmapworld_specificroom, QS</t>
-        </is>
-      </c>
-      <c r="AV4" s="3" t="inlineStr">
-        <is>
-          <t>ID_wordle, %P</t>
-        </is>
-      </c>
-      <c r="AW4" s="3" t="inlineStr">
-        <is>
-          <t>ID_wordle, QS</t>
-        </is>
-      </c>
-      <c r="AX4" s="3" t="inlineStr">
-        <is>
-          <t>ID_wordle_withclue, %P</t>
-        </is>
-      </c>
-      <c r="AY4" s="3" t="inlineStr">
-        <is>
-          <t>ID_wordle_withclue, QS</t>
-        </is>
-      </c>
-      <c r="AZ4" s="3" t="inlineStr">
-        <is>
-          <t>ID_wordle_withcritic, %P</t>
-        </is>
-      </c>
-      <c r="BA4" s="3" t="inlineStr">
-        <is>
-          <t>ID_wordle_withcritic, QS</t>
-        </is>
-      </c>
-      <c r="BB4" s="3" t="inlineStr">
-        <is>
-          <t>OOD_chronicle, %P</t>
-        </is>
-      </c>
-      <c r="BC4" s="3" t="inlineStr">
-        <is>
-          <t>OOD_chronicle, QS</t>
-        </is>
-      </c>
-      <c r="BD4" s="3" t="inlineStr">
-        <is>
-          <t>OOD_clockwork_courier, %P</t>
-        </is>
-      </c>
-      <c r="BE4" s="3" t="inlineStr">
-        <is>
-          <t>OOD_clockwork_courier, QS</t>
-        </is>
-      </c>
-      <c r="BF4" s="3" t="inlineStr">
-        <is>
-          <t>OOD_cryptolect, %P</t>
-        </is>
-      </c>
-      <c r="BG4" s="3" t="inlineStr">
-        <is>
-          <t>OOD_cryptolect, QS</t>
-        </is>
-      </c>
-      <c r="BH4" s="3" t="inlineStr">
-        <is>
-          <t>OOD_get_to_the_point, %P</t>
-        </is>
-      </c>
-      <c r="BI4" s="3" t="inlineStr">
-        <is>
-          <t>OOD_get_to_the_point, QS</t>
-        </is>
-      </c>
-      <c r="BJ4" s="3" t="inlineStr">
-        <is>
-          <t>OOD_st_clean_up, %P</t>
-        </is>
-      </c>
-      <c r="BK4" s="3" t="inlineStr">
-        <is>
-          <t>OOD_st_clean_up, QS</t>
-        </is>
-      </c>
-      <c r="BL4" s="3" t="inlineStr">
-        <is>
-          <t>OOD_ta_blackjack, %P</t>
-        </is>
-      </c>
-      <c r="BM4" s="3" t="inlineStr">
-        <is>
-          <t>OOD_ta_blackjack, QS</t>
-        </is>
-      </c>
-      <c r="BN4" s="3" t="inlineStr">
-        <is>
-          <t>OOD_ta_frozen_lake, %P</t>
-        </is>
-      </c>
-      <c r="BO4" s="3" t="inlineStr">
-        <is>
-          <t>OOD_ta_frozen_lake, QS</t>
-        </is>
-      </c>
-      <c r="BP4" s="3" t="inlineStr">
-        <is>
-          <t>OOD_ta_mastermind, %P</t>
-        </is>
-      </c>
-      <c r="BQ4" s="3" t="inlineStr">
-        <is>
-          <t>OOD_ta_mastermind, QS</t>
-        </is>
-      </c>
-      <c r="BR4" s="3" t="inlineStr">
-        <is>
-          <t>OOD_ta_sokoban, %P</t>
-        </is>
-      </c>
-      <c r="BS4" s="3" t="inlineStr">
-        <is>
-          <t>OOD_ta_sokoban, QS</t>
-        </is>
-      </c>
-      <c r="BT4" s="3" t="inlineStr">
-        <is>
-          <t>OOD_toh_multi_turn, %P</t>
-        </is>
-      </c>
-      <c r="BU4" s="3" t="inlineStr">
-        <is>
-          <t>OOD_toh_multi_turn, QS</t>
-        </is>
-      </c>
-      <c r="BV4" s="3" t="inlineStr">
-        <is>
-          <t>OOD_wordle-crazy, %P</t>
-        </is>
-      </c>
-      <c r="BW4" s="3" t="inlineStr">
-        <is>
-          <t>OOD_wordle-crazy, QS</t>
-        </is>
-      </c>
-      <c r="BX4" s="3" t="inlineStr">
-        <is>
-          <t>OOD_wordle-crazy_withclue, %P</t>
-        </is>
-      </c>
-      <c r="BY4" s="3" t="inlineStr">
-        <is>
-          <t>OOD_wordle-crazy_withclue, QS</t>
-        </is>
-      </c>
-      <c r="BZ4" s="3" t="inlineStr">
-        <is>
-          <t>OOD_wordle-crazy_withcritic, %P</t>
-        </is>
-      </c>
-      <c r="CA4" s="3" t="inlineStr">
-        <is>
-          <t>OOD_wordle-crazy_withcritic, QS</t>
-        </is>
+    <row r="4" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="W4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="X4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AK4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AL4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AN4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AO4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AQ4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AR4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AS4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AT4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AU4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AV4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AW4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AX4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AY4" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="AZ4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="BA4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="BB4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="BC4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="BD4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="BE4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="BF4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="BG4" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="BH4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="BI4" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="BJ4" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="BK4" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="BL4" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="BM4" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="BN4" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="BO4" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="BP4" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="BQ4" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="BR4" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="BS4" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="BT4" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="BU4" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="BV4" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="BW4" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="BX4" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="BY4" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="BZ4" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="CA4" s="3" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>qwen3.5-2b</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
       <c r="D5" s="6" t="n">
-        <v>11.43</v>
+        <v>10.67</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>44.24</v>
@@ -906,7 +1189,9 @@
       <c r="L5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="7" t="n"/>
+      <c r="M5" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="N5" s="6" t="n">
         <v>100</v>
       </c>
@@ -928,7 +1213,9 @@
       <c r="T5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U5" s="7" t="n"/>
+      <c r="U5" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="V5" s="6" t="n">
         <v>30</v>
       </c>
@@ -944,7 +1231,9 @@
       <c r="Z5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="7" t="n"/>
+      <c r="AA5" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="AB5" s="6" t="n">
         <v>100</v>
       </c>
@@ -972,7 +1261,9 @@
       <c r="AJ5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="AK5" s="7" t="n"/>
+      <c r="AK5" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="AL5" s="6" t="n">
         <v>100</v>
       </c>
@@ -983,20 +1274,26 @@
         <v>93.33</v>
       </c>
       <c r="AO5" s="6" t="n">
-        <v>8.630000000000001</v>
+        <v>8.63</v>
       </c>
       <c r="AP5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="AQ5" s="7" t="n"/>
+      <c r="AQ5" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="AR5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="AS5" s="7" t="n"/>
+      <c r="AS5" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="AT5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="AU5" s="7" t="n"/>
+      <c r="AU5" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="AV5" s="6" t="n">
         <v>16.67</v>
       </c>
@@ -1024,7 +1321,9 @@
       <c r="BD5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="BE5" s="7" t="n"/>
+      <c r="BE5" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="BF5" s="6" t="n">
         <v>56.67</v>
       </c>
@@ -1058,7 +1357,9 @@
       <c r="BP5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="BQ5" s="7" t="n"/>
+      <c r="BQ5" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="BR5" s="6" t="n">
         <v>10</v>
       </c>
@@ -1090,26 +1391,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>CityUoL__qwen3.5-2b__Qwen-GuidePlay-2B-v1</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>CityUoL</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Qwen-GuidePlay-2B-v1</t>
-        </is>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>84</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>39.01</v>
-      </c>
-      <c r="E6" s="14" t="n">
+        <v>35.99</v>
+      </c>
+      <c r="E6" s="11" t="n">
         <v>-1.94</v>
       </c>
       <c r="F6" s="10" t="n">
@@ -1133,17 +1428,19 @@
       <c r="L6" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="M6" s="16" t="n"/>
-      <c r="N6" s="12" t="n">
+      <c r="M6" s="12" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="N6" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O6" s="10" t="n">
         <v>34.62</v>
       </c>
-      <c r="P6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="12" t="n">
+      <c r="P6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R6" s="10" t="n">
@@ -1155,27 +1452,31 @@
       <c r="T6" s="10" t="n">
         <v>67.69</v>
       </c>
-      <c r="U6" s="16" t="n"/>
+      <c r="U6" s="12" t="n">
+        <v>36.36</v>
+      </c>
       <c r="V6" s="10" t="n">
         <v>70</v>
       </c>
       <c r="W6" s="10" t="n">
         <v>69.19</v>
       </c>
-      <c r="X6" s="14" t="n">
+      <c r="X6" s="11" t="n">
         <v>-8</v>
       </c>
-      <c r="Y6" s="14" t="n">
+      <c r="Y6" s="11" t="n">
         <v>-15</v>
       </c>
       <c r="Z6" s="10" t="n">
         <v>98.33</v>
       </c>
-      <c r="AA6" s="16" t="n"/>
-      <c r="AB6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="14" t="n">
+      <c r="AA6" s="12" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="AB6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="11" t="n">
         <v>-20</v>
       </c>
       <c r="AD6" s="10" t="n">
@@ -1184,13 +1485,13 @@
       <c r="AE6" s="10" t="n">
         <v>82.27</v>
       </c>
-      <c r="AF6" s="12" t="n">
+      <c r="AF6" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AG6" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="AH6" s="12" t="n">
+      <c r="AH6" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AI6" s="10" t="n">
@@ -1199,8 +1500,10 @@
       <c r="AJ6" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="AK6" s="16" t="n"/>
-      <c r="AL6" s="12" t="n">
+      <c r="AK6" s="12" t="n">
+        <v>53.77</v>
+      </c>
+      <c r="AL6" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AM6" s="10" t="n">
@@ -1215,15 +1518,21 @@
       <c r="AP6" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="AQ6" s="16" t="n"/>
+      <c r="AQ6" s="12" t="n">
+        <v>75.77</v>
+      </c>
       <c r="AR6" s="10" t="n">
         <v>90</v>
       </c>
-      <c r="AS6" s="16" t="n"/>
+      <c r="AS6" s="12" t="n">
+        <v>69.81</v>
+      </c>
       <c r="AT6" s="10" t="n">
         <v>96.67</v>
       </c>
-      <c r="AU6" s="16" t="n"/>
+      <c r="AU6" s="12" t="n">
+        <v>100</v>
+      </c>
       <c r="AV6" s="10" t="n">
         <v>33.33</v>
       </c>
@@ -1242,64 +1551,70 @@
       <c r="BA6" s="10" t="n">
         <v>75</v>
       </c>
-      <c r="BB6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC6" s="14" t="n">
+      <c r="BB6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" s="11" t="n">
         <v>-1.69</v>
       </c>
       <c r="BD6" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="BE6" s="16" t="n"/>
+      <c r="BE6" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="BF6" s="10" t="n">
         <v>43.33</v>
       </c>
-      <c r="BG6" s="12" t="n">
+      <c r="BG6" s="13" t="n">
         <v>0</v>
       </c>
       <c r="BH6" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="BI6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ6" s="14" t="n">
+      <c r="BI6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" s="11" t="n">
         <v>-16.66</v>
       </c>
-      <c r="BK6" s="14" t="n">
+      <c r="BK6" s="11" t="n">
         <v>-1.85</v>
       </c>
-      <c r="BL6" s="14" t="n">
+      <c r="BL6" s="11" t="n">
         <v>-80</v>
       </c>
-      <c r="BM6" s="16" t="n"/>
+      <c r="BM6" s="15" t="n">
+        <v>-23.33</v>
+      </c>
       <c r="BN6" s="10" t="n">
         <v>20</v>
       </c>
       <c r="BO6" s="10" t="n">
         <v>4.64</v>
       </c>
-      <c r="BP6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ6" s="16" t="n"/>
-      <c r="BR6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT6" s="14" t="n">
+      <c r="BP6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT6" s="11" t="n">
         <v>-20.83</v>
       </c>
-      <c r="BU6" s="12" t="n">
+      <c r="BU6" s="13" t="n">
         <v>0</v>
       </c>
       <c r="BV6" s="10" t="n">
         <v>13.34</v>
       </c>
-      <c r="BW6" s="12" t="n">
+      <c r="BW6" s="13" t="n">
         <v>0</v>
       </c>
       <c r="BX6" s="10" t="n">
@@ -1312,29 +1627,23 @@
         <v>70</v>
       </c>
       <c r="CA6" s="10" t="n">
-        <v>95.65000000000001</v>
+        <v>95.65</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>DAIR__qwen3.5-2b__sft-dpo-v2</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>DAIR</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>sft-dpo-v2</t>
-        </is>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>87</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="E7" s="14" t="n">
+        <v>38.93</v>
+      </c>
+      <c r="E7" s="11" t="n">
         <v>-0.71</v>
       </c>
       <c r="F7" s="10" t="n">
@@ -1358,17 +1667,19 @@
       <c r="L7" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="M7" s="16" t="n"/>
-      <c r="N7" s="12" t="n">
+      <c r="M7" s="12" t="n">
+        <v>93.06</v>
+      </c>
+      <c r="N7" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O7" s="10" t="n">
         <v>10.58</v>
       </c>
-      <c r="P7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="14" t="n">
+      <c r="P7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="11" t="n">
         <v>-3</v>
       </c>
       <c r="R7" s="10" t="n">
@@ -1380,7 +1691,9 @@
       <c r="T7" s="10" t="n">
         <v>75.38</v>
       </c>
-      <c r="U7" s="16" t="n"/>
+      <c r="U7" s="12" t="n">
+        <v>35.71</v>
+      </c>
       <c r="V7" s="10" t="n">
         <v>70</v>
       </c>
@@ -1396,11 +1709,13 @@
       <c r="Z7" s="10" t="n">
         <v>96.67</v>
       </c>
-      <c r="AA7" s="16" t="n"/>
-      <c r="AB7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="14" t="n">
+      <c r="AA7" s="12" t="n">
+        <v>55.17</v>
+      </c>
+      <c r="AB7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="11" t="n">
         <v>-23</v>
       </c>
       <c r="AD7" s="10" t="n">
@@ -1409,13 +1724,13 @@
       <c r="AE7" s="10" t="n">
         <v>85.95</v>
       </c>
-      <c r="AF7" s="12" t="n">
+      <c r="AF7" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AG7" s="10" t="n">
         <v>22.5</v>
       </c>
-      <c r="AH7" s="12" t="n">
+      <c r="AH7" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AI7" s="10" t="n">
@@ -1424,8 +1739,10 @@
       <c r="AJ7" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="AK7" s="16" t="n"/>
-      <c r="AL7" s="12" t="n">
+      <c r="AK7" s="12" t="n">
+        <v>57.09</v>
+      </c>
+      <c r="AL7" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AM7" s="10" t="n">
@@ -1440,15 +1757,21 @@
       <c r="AP7" s="10" t="n">
         <v>90</v>
       </c>
-      <c r="AQ7" s="16" t="n"/>
+      <c r="AQ7" s="12" t="n">
+        <v>72.24</v>
+      </c>
       <c r="AR7" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="AS7" s="16" t="n"/>
+      <c r="AS7" s="12" t="n">
+        <v>75.48</v>
+      </c>
       <c r="AT7" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="AU7" s="16" t="n"/>
+      <c r="AU7" s="12" t="n">
+        <v>100</v>
+      </c>
       <c r="AV7" s="10" t="n">
         <v>23.33</v>
       </c>
@@ -1458,7 +1781,7 @@
       <c r="AX7" s="10" t="n">
         <v>23.33</v>
       </c>
-      <c r="AY7" s="12" t="n">
+      <c r="AY7" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AZ7" s="10" t="n">
@@ -1467,29 +1790,31 @@
       <c r="BA7" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="BB7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC7" s="14" t="n">
+      <c r="BB7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" s="11" t="n">
         <v>-3.35</v>
       </c>
       <c r="BD7" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="BE7" s="16" t="n"/>
+      <c r="BE7" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="BF7" s="10" t="n">
         <v>23.33</v>
       </c>
-      <c r="BG7" s="12" t="n">
+      <c r="BG7" s="13" t="n">
         <v>0</v>
       </c>
       <c r="BH7" s="10" t="n">
         <v>57.5</v>
       </c>
-      <c r="BI7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ7" s="14" t="n">
+      <c r="BI7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" s="11" t="n">
         <v>-33.33</v>
       </c>
       <c r="BK7" s="10" t="n">
@@ -1507,20 +1832,22 @@
       <c r="BO7" s="10" t="n">
         <v>13.21</v>
       </c>
-      <c r="BP7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ7" s="16" t="n"/>
+      <c r="BP7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ7" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="BR7" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="BS7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT7" s="14" t="n">
+      <c r="BS7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" s="11" t="n">
         <v>-20.83</v>
       </c>
-      <c r="BU7" s="12" t="n">
+      <c r="BU7" s="13" t="n">
         <v>0</v>
       </c>
       <c r="BV7" s="10" t="n">
@@ -1542,24 +1869,18 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>DAIR__qwen3.5-2b__sft-v1</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>DAIR</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>sft-v1</t>
-        </is>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>89</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>34.91</v>
+        <v>35.34</v>
       </c>
       <c r="E8" s="10" t="n">
         <v>0.11</v>
@@ -1585,17 +1906,19 @@
       <c r="L8" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="M8" s="16" t="n"/>
-      <c r="N8" s="12" t="n">
+      <c r="M8" s="12" t="n">
+        <v>95</v>
+      </c>
+      <c r="N8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O8" s="10" t="n">
         <v>5.77</v>
       </c>
-      <c r="P8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="14" t="n">
+      <c r="P8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="11" t="n">
         <v>-2</v>
       </c>
       <c r="R8" s="10" t="n">
@@ -1607,7 +1930,9 @@
       <c r="T8" s="10" t="n">
         <v>64.62</v>
       </c>
-      <c r="U8" s="16" t="n"/>
+      <c r="U8" s="12" t="n">
+        <v>39.29</v>
+      </c>
       <c r="V8" s="10" t="n">
         <v>70</v>
       </c>
@@ -1623,11 +1948,13 @@
       <c r="Z8" s="10" t="n">
         <v>98.33</v>
       </c>
-      <c r="AA8" s="16" t="n"/>
-      <c r="AB8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="14" t="n">
+      <c r="AA8" s="12" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="AB8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="11" t="n">
         <v>-23</v>
       </c>
       <c r="AD8" s="10" t="n">
@@ -1636,13 +1963,13 @@
       <c r="AE8" s="10" t="n">
         <v>84.92</v>
       </c>
-      <c r="AF8" s="12" t="n">
+      <c r="AF8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AG8" s="10" t="n">
         <v>17.5</v>
       </c>
-      <c r="AH8" s="12" t="n">
+      <c r="AH8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AI8" s="10" t="n">
@@ -1651,8 +1978,10 @@
       <c r="AJ8" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="AK8" s="16" t="n"/>
-      <c r="AL8" s="12" t="n">
+      <c r="AK8" s="12" t="n">
+        <v>49.95</v>
+      </c>
+      <c r="AL8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AM8" s="10" t="n">
@@ -1667,15 +1996,21 @@
       <c r="AP8" s="10" t="n">
         <v>78</v>
       </c>
-      <c r="AQ8" s="16" t="n"/>
+      <c r="AQ8" s="12" t="n">
+        <v>73.28</v>
+      </c>
       <c r="AR8" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="AS8" s="16" t="n"/>
+      <c r="AS8" s="12" t="n">
+        <v>74.95</v>
+      </c>
       <c r="AT8" s="10" t="n">
         <v>96.67</v>
       </c>
-      <c r="AU8" s="16" t="n"/>
+      <c r="AU8" s="12" t="n">
+        <v>100</v>
+      </c>
       <c r="AV8" s="10" t="n">
         <v>16.66</v>
       </c>
@@ -1685,7 +2020,7 @@
       <c r="AX8" s="10" t="n">
         <v>16.66</v>
       </c>
-      <c r="AY8" s="14" t="n">
+      <c r="AY8" s="11" t="n">
         <v>-14.29</v>
       </c>
       <c r="AZ8" s="10" t="n">
@@ -1694,35 +2029,37 @@
       <c r="BA8" s="10" t="n">
         <v>75</v>
       </c>
-      <c r="BB8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC8" s="14" t="n">
+      <c r="BB8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" s="11" t="n">
         <v>-1.24</v>
       </c>
       <c r="BD8" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="BE8" s="16" t="n"/>
+      <c r="BE8" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="BF8" s="10" t="n">
         <v>3.33</v>
       </c>
-      <c r="BG8" s="12" t="n">
+      <c r="BG8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="BH8" s="10" t="n">
         <v>57.5</v>
       </c>
-      <c r="BI8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ8" s="12" t="n">
+      <c r="BI8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="BK8" s="10" t="n">
         <v>3.62</v>
       </c>
-      <c r="BL8" s="12" t="n">
+      <c r="BL8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="BM8" s="10" t="n">
@@ -1737,15 +2074,19 @@
       <c r="BP8" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="BQ8" s="16" t="n"/>
-      <c r="BR8" s="14" t="n">
+      <c r="BQ8" s="12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BR8" s="11" t="n">
         <v>-10</v>
       </c>
-      <c r="BS8" s="16" t="n"/>
-      <c r="BT8" s="14" t="n">
+      <c r="BS8" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" s="11" t="n">
         <v>-8.33</v>
       </c>
-      <c r="BU8" s="12" t="n">
+      <c r="BU8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="BV8" s="10" t="n">
@@ -1767,26 +2108,20 @@
         <v>96.3</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>playornotplay__qwen3.5-2b__playornotplay-v1.0-merged-fp32-828e356</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>playornotplay</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>playornotplay-v1.0-merged-fp32-7263076</t>
-        </is>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>92</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>28.47</v>
-      </c>
-      <c r="E9" s="14" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="E9" s="11" t="n">
         <v>-0.1</v>
       </c>
       <c r="F9" s="10" t="n">
@@ -1801,7 +2136,7 @@
       <c r="I9" s="10" t="n">
         <v>4.16</v>
       </c>
-      <c r="J9" s="14" t="n">
+      <c r="J9" s="11" t="n">
         <v>-2.11</v>
       </c>
       <c r="K9" s="10" t="n">
@@ -1810,17 +2145,19 @@
       <c r="L9" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="M9" s="16" t="n"/>
-      <c r="N9" s="12" t="n">
+      <c r="M9" s="12" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="N9" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O9" s="10" t="n">
         <v>39.42</v>
       </c>
-      <c r="P9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="14" t="n">
+      <c r="P9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="11" t="n">
         <v>-2</v>
       </c>
       <c r="R9" s="10" t="n">
@@ -1832,27 +2169,31 @@
       <c r="T9" s="10" t="n">
         <v>46.92</v>
       </c>
-      <c r="U9" s="16" t="n"/>
+      <c r="U9" s="12" t="n">
+        <v>29.51</v>
+      </c>
       <c r="V9" s="10" t="n">
         <v>70</v>
       </c>
       <c r="W9" s="10" t="n">
         <v>39.75</v>
       </c>
-      <c r="X9" s="14" t="n">
+      <c r="X9" s="11" t="n">
         <v>-8</v>
       </c>
-      <c r="Y9" s="14" t="n">
+      <c r="Y9" s="11" t="n">
         <v>-11.11</v>
       </c>
       <c r="Z9" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="AA9" s="16" t="n"/>
-      <c r="AB9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="14" t="n">
+      <c r="AA9" s="12" t="n">
+        <v>18.33</v>
+      </c>
+      <c r="AB9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="11" t="n">
         <v>-14</v>
       </c>
       <c r="AD9" s="10" t="n">
@@ -1861,13 +2202,13 @@
       <c r="AE9" s="10" t="n">
         <v>59.43</v>
       </c>
-      <c r="AF9" s="12" t="n">
+      <c r="AF9" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AG9" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="AH9" s="12" t="n">
+      <c r="AH9" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AI9" s="10" t="n">
@@ -1876,11 +2217,13 @@
       <c r="AJ9" s="10" t="n">
         <v>56</v>
       </c>
-      <c r="AK9" s="16" t="n"/>
-      <c r="AL9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" s="14" t="n">
+      <c r="AK9" s="12" t="n">
+        <v>38.69</v>
+      </c>
+      <c r="AL9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="11" t="n">
         <v>-2.23</v>
       </c>
       <c r="AN9" s="10" t="n">
@@ -1892,15 +2235,21 @@
       <c r="AP9" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="AQ9" s="16" t="n"/>
+      <c r="AQ9" s="12" t="n">
+        <v>57.91</v>
+      </c>
       <c r="AR9" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="AS9" s="16" t="n"/>
+      <c r="AS9" s="12" t="n">
+        <v>70.99</v>
+      </c>
       <c r="AT9" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="AU9" s="16" t="n"/>
+      <c r="AU9" s="12" t="n">
+        <v>53.33</v>
+      </c>
       <c r="AV9" s="10" t="n">
         <v>26.66</v>
       </c>
@@ -1913,47 +2262,49 @@
       <c r="AY9" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="AZ9" s="12" t="n">
+      <c r="AZ9" s="13" t="n">
         <v>0</v>
       </c>
       <c r="BA9" s="10" t="n">
         <v>100</v>
       </c>
-      <c r="BB9" s="14" t="n">
+      <c r="BB9" s="11" t="n">
         <v>-96.67</v>
       </c>
-      <c r="BC9" s="14" t="n">
+      <c r="BC9" s="11" t="n">
         <v>-5.02</v>
       </c>
       <c r="BD9" s="10" t="n">
         <v>56.67</v>
       </c>
-      <c r="BE9" s="16" t="n"/>
-      <c r="BF9" s="14" t="n">
+      <c r="BE9" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" s="11" t="n">
         <v>-23.34</v>
       </c>
       <c r="BG9" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="BH9" s="14" t="n">
+      <c r="BH9" s="11" t="n">
         <v>-5</v>
       </c>
-      <c r="BI9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ9" s="14" t="n">
+      <c r="BI9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ9" s="11" t="n">
         <v>-50</v>
       </c>
-      <c r="BK9" s="14" t="n">
+      <c r="BK9" s="11" t="n">
         <v>-6.8</v>
       </c>
-      <c r="BL9" s="14" t="n">
+      <c r="BL9" s="11" t="n">
         <v>-55</v>
       </c>
-      <c r="BM9" s="14" t="n">
+      <c r="BM9" s="11" t="n">
         <v>-4.66</v>
       </c>
-      <c r="BN9" s="14" t="n">
+      <c r="BN9" s="11" t="n">
         <v>-10</v>
       </c>
       <c r="BO9" s="10" t="n">
@@ -1962,17 +2313,19 @@
       <c r="BP9" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="BQ9" s="16" t="n"/>
-      <c r="BR9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS9" s="12" t="n">
+      <c r="BQ9" s="12" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="BR9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" s="13" t="n">
         <v>0</v>
       </c>
       <c r="BT9" s="10" t="n">
         <v>4.17</v>
       </c>
-      <c r="BU9" s="12" t="n">
+      <c r="BU9" s="13" t="n">
         <v>0</v>
       </c>
       <c r="BV9" s="10" t="n">
@@ -1994,16 +2347,14 @@
         <v>90.91</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>qwen3.5-4b</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
       <c r="D10" s="6" t="n">
-        <v>33.71</v>
+        <v>26.66</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>51.33</v>
@@ -2053,7 +2404,9 @@
       <c r="T10" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U10" s="7" t="n"/>
+      <c r="U10" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="V10" s="6" t="n">
         <v>72.5</v>
       </c>
@@ -2064,12 +2417,14 @@
         <v>98</v>
       </c>
       <c r="Y10" s="6" t="n">
-        <v>68.68000000000001</v>
+        <v>68.68</v>
       </c>
       <c r="Z10" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="AA10" s="7" t="n"/>
+      <c r="AA10" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="AB10" s="6" t="n">
         <v>100</v>
       </c>
@@ -2199,7 +2554,9 @@
       <c r="BR10" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="BS10" s="7" t="n"/>
+      <c r="BS10" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="BT10" s="6" t="n">
         <v>54.17</v>
       </c>
@@ -2225,24 +2582,18 @@
         <v>83.33</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Bentel rockers__qwen3.5-4b__Bentel_iter</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Bentel rockers</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Bentel_iter</t>
-        </is>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>96</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>2.38</v>
+        <v>4.92</v>
       </c>
       <c r="E11" s="10" t="n">
         <v>2.94</v>
@@ -2256,81 +2607,85 @@
       <c r="H11" s="10" t="n">
         <v>0.86</v>
       </c>
-      <c r="I11" s="14" t="n">
+      <c r="I11" s="11" t="n">
         <v>-1.39</v>
       </c>
       <c r="J11" s="10" t="n">
         <v>1.48</v>
       </c>
-      <c r="K11" s="14" t="n">
+      <c r="K11" s="11" t="n">
         <v>-4.2</v>
       </c>
       <c r="L11" s="10" t="n">
         <v>17.5</v>
       </c>
-      <c r="M11" s="14" t="n">
+      <c r="M11" s="11" t="n">
         <v>-17.01</v>
       </c>
-      <c r="N11" s="12" t="n">
+      <c r="N11" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O11" s="10" t="n">
         <v>20.19</v>
       </c>
-      <c r="P11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="14" t="n">
+      <c r="P11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="11" t="n">
         <v>-2</v>
       </c>
       <c r="R11" s="10" t="n">
         <v>27.77</v>
       </c>
-      <c r="S11" s="14" t="n">
+      <c r="S11" s="11" t="n">
         <v>-0.64</v>
       </c>
       <c r="T11" s="10" t="n">
         <v>19.23</v>
       </c>
-      <c r="U11" s="16" t="n"/>
+      <c r="U11" s="12" t="n">
+        <v>28</v>
+      </c>
       <c r="V11" s="10" t="n">
         <v>7.5</v>
       </c>
       <c r="W11" s="10" t="n">
         <v>14.24</v>
       </c>
-      <c r="X11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="14" t="n">
+      <c r="X11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="11" t="n">
         <v>-1.28</v>
       </c>
       <c r="Z11" s="10" t="n">
         <v>93.33</v>
       </c>
-      <c r="AA11" s="16" t="n"/>
-      <c r="AB11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="14" t="n">
+      <c r="AA11" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="11" t="n">
         <v>-5</v>
       </c>
-      <c r="AD11" s="14" t="n">
+      <c r="AD11" s="11" t="n">
         <v>-27.5</v>
       </c>
-      <c r="AE11" s="14" t="n">
+      <c r="AE11" s="11" t="n">
         <v>-11.59</v>
       </c>
-      <c r="AF11" s="12" t="n">
+      <c r="AF11" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AG11" s="10" t="n">
         <v>12.5</v>
       </c>
-      <c r="AH11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" s="14" t="n">
+      <c r="AH11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="11" t="n">
         <v>-4</v>
       </c>
       <c r="AJ11" s="10" t="n">
@@ -2339,25 +2694,25 @@
       <c r="AK11" s="10" t="n">
         <v>7.04</v>
       </c>
-      <c r="AL11" s="14" t="n">
+      <c r="AL11" s="11" t="n">
         <v>-3.33</v>
       </c>
       <c r="AM11" s="10" t="n">
         <v>14.49</v>
       </c>
-      <c r="AN11" s="14" t="n">
+      <c r="AN11" s="11" t="n">
         <v>-8.33</v>
       </c>
       <c r="AO11" s="10" t="n">
         <v>6.01</v>
       </c>
-      <c r="AP11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" s="14" t="n">
+      <c r="AP11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="11" t="n">
         <v>-1.19</v>
       </c>
-      <c r="AR11" s="14" t="n">
+      <c r="AR11" s="11" t="n">
         <v>-20</v>
       </c>
       <c r="AS11" s="10" t="n">
@@ -2366,20 +2721,22 @@
       <c r="AT11" s="10" t="n">
         <v>33.34</v>
       </c>
-      <c r="AU11" s="14" t="n">
+      <c r="AU11" s="11" t="n">
         <v>-5.29</v>
       </c>
-      <c r="AV11" s="14" t="n">
+      <c r="AV11" s="11" t="n">
         <v>-26.67</v>
       </c>
-      <c r="AW11" s="16" t="n"/>
+      <c r="AW11" s="15" t="n">
+        <v>-25</v>
+      </c>
       <c r="AX11" s="10" t="n">
         <v>3.33</v>
       </c>
-      <c r="AY11" s="14" t="n">
+      <c r="AY11" s="11" t="n">
         <v>-13.89</v>
       </c>
-      <c r="AZ11" s="14" t="n">
+      <c r="AZ11" s="11" t="n">
         <v>-3.33</v>
       </c>
       <c r="BA11" s="10" t="n">
@@ -2388,16 +2745,16 @@
       <c r="BB11" s="10" t="n">
         <v>3.33</v>
       </c>
-      <c r="BC11" s="14" t="n">
+      <c r="BC11" s="11" t="n">
         <v>-1.9</v>
       </c>
       <c r="BD11" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="BE11" s="14" t="n">
+      <c r="BE11" s="11" t="n">
         <v>-14.58</v>
       </c>
-      <c r="BF11" s="14" t="n">
+      <c r="BF11" s="11" t="n">
         <v>-10</v>
       </c>
       <c r="BG11" s="10" t="n">
@@ -2406,10 +2763,10 @@
       <c r="BH11" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="BI11" s="14" t="n">
+      <c r="BI11" s="11" t="n">
         <v>-8.08</v>
       </c>
-      <c r="BJ11" s="14" t="n">
+      <c r="BJ11" s="11" t="n">
         <v>-33.33</v>
       </c>
       <c r="BK11" s="10" t="n">
@@ -2421,26 +2778,28 @@
       <c r="BM11" s="10" t="n">
         <v>0.35</v>
       </c>
-      <c r="BN11" s="14" t="n">
+      <c r="BN11" s="11" t="n">
         <v>-6.67</v>
       </c>
-      <c r="BO11" s="14" t="n">
+      <c r="BO11" s="11" t="n">
         <v>-15.49</v>
       </c>
-      <c r="BP11" s="14" t="n">
+      <c r="BP11" s="11" t="n">
         <v>-20</v>
       </c>
-      <c r="BQ11" s="12" t="n">
+      <c r="BQ11" s="13" t="n">
         <v>0</v>
       </c>
       <c r="BR11" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="BS11" s="16" t="n"/>
-      <c r="BT11" s="14" t="n">
+      <c r="BS11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT11" s="11" t="n">
         <v>-20.84</v>
       </c>
-      <c r="BU11" s="14" t="n">
+      <c r="BU11" s="11" t="n">
         <v>-12.5</v>
       </c>
       <c r="BV11" s="10" t="n">
@@ -2452,104 +2811,102 @@
       <c r="BX11" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="BY11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ11" s="14" t="n">
+      <c r="BY11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ11" s="11" t="n">
         <v>-6.67</v>
       </c>
       <c r="CA11" s="10" t="n">
         <v>16.67</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>Bentel rockers__qwen3.5-4b__Bentel_iter_2</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Bentel rockers</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Bentel_iter_2</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="n">
-        <v>-4.04</v>
-      </c>
-      <c r="E12" s="14" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>-2.39</v>
+      </c>
+      <c r="E12" s="11" t="n">
         <v>-3.96</v>
       </c>
-      <c r="F12" s="14" t="n">
+      <c r="F12" s="11" t="n">
         <v>-2.05</v>
       </c>
       <c r="G12" s="10" t="n">
         <v>10.39</v>
       </c>
-      <c r="H12" s="14" t="n">
+      <c r="H12" s="11" t="n">
         <v>-9.35</v>
       </c>
-      <c r="I12" s="14" t="n">
+      <c r="I12" s="11" t="n">
         <v>-7.8</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>9.359999999999999</v>
-      </c>
-      <c r="K12" s="14" t="n">
+        <v>9.36</v>
+      </c>
+      <c r="K12" s="11" t="n">
         <v>-20.94</v>
       </c>
       <c r="L12" s="10" t="n">
         <v>7.5</v>
       </c>
-      <c r="M12" s="14" t="n">
+      <c r="M12" s="11" t="n">
         <v>-64.27</v>
       </c>
-      <c r="N12" s="12" t="n">
+      <c r="N12" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O12" s="10" t="n">
         <v>30.77</v>
       </c>
-      <c r="P12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="12" t="n">
+      <c r="P12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R12" s="10" t="n">
         <v>44.44</v>
       </c>
-      <c r="S12" s="14" t="n">
+      <c r="S12" s="11" t="n">
         <v>-24.73</v>
       </c>
-      <c r="T12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="16" t="n"/>
+      <c r="T12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="V12" s="10" t="n">
         <v>17.5</v>
       </c>
-      <c r="W12" s="14" t="n">
+      <c r="W12" s="11" t="n">
         <v>-3.6</v>
       </c>
       <c r="X12" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="Y12" s="14" t="n">
+      <c r="Y12" s="11" t="n">
         <v>-6.79</v>
       </c>
       <c r="Z12" s="10" t="n">
         <v>98.33</v>
       </c>
-      <c r="AA12" s="16" t="n"/>
-      <c r="AB12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="14" t="n">
+      <c r="AA12" s="12" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="AB12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="11" t="n">
         <v>-46</v>
       </c>
       <c r="AD12" s="10" t="n">
@@ -2558,16 +2915,16 @@
       <c r="AE12" s="10" t="n">
         <v>23.16</v>
       </c>
-      <c r="AF12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="14" t="n">
+      <c r="AF12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="11" t="n">
         <v>-15</v>
       </c>
-      <c r="AH12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="14" t="n">
+      <c r="AH12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="11" t="n">
         <v>-4</v>
       </c>
       <c r="AJ12" s="10" t="n">
@@ -2576,28 +2933,30 @@
       <c r="AK12" s="10" t="n">
         <v>2.92</v>
       </c>
-      <c r="AL12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" s="14" t="n">
+      <c r="AL12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" s="11" t="n">
         <v>-5.83</v>
       </c>
-      <c r="AP12" s="14" t="n">
+      <c r="AP12" s="11" t="n">
         <v>-2</v>
       </c>
       <c r="AQ12" s="10" t="n">
         <v>4.07</v>
       </c>
-      <c r="AR12" s="14" t="n">
+      <c r="AR12" s="11" t="n">
         <v>-70</v>
       </c>
-      <c r="AS12" s="16" t="n"/>
+      <c r="AS12" s="15" t="n">
+        <v>-59.57</v>
+      </c>
       <c r="AT12" s="10" t="n">
         <v>20</v>
       </c>
@@ -2607,116 +2966,112 @@
       <c r="AV12" s="10" t="n">
         <v>16.66</v>
       </c>
-      <c r="AW12" s="14" t="n">
+      <c r="AW12" s="11" t="n">
         <v>-23.46</v>
       </c>
       <c r="AX12" s="10" t="n">
         <v>16.66</v>
       </c>
-      <c r="AY12" s="14" t="n">
+      <c r="AY12" s="11" t="n">
         <v>-25</v>
       </c>
       <c r="AZ12" s="10" t="n">
         <v>26.67</v>
       </c>
-      <c r="BA12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" s="14" t="n">
+      <c r="BA12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" s="11" t="n">
         <v>-10</v>
       </c>
-      <c r="BC12" s="14" t="n">
+      <c r="BC12" s="11" t="n">
         <v>-5.12</v>
       </c>
       <c r="BD12" s="10" t="n">
         <v>63.33</v>
       </c>
-      <c r="BE12" s="14" t="n">
+      <c r="BE12" s="11" t="n">
         <v>-23.33</v>
       </c>
       <c r="BF12" s="10" t="n">
         <v>23.34</v>
       </c>
-      <c r="BG12" s="14" t="n">
+      <c r="BG12" s="11" t="n">
         <v>-7</v>
       </c>
       <c r="BH12" s="10" t="n">
         <v>17.5</v>
       </c>
-      <c r="BI12" s="14" t="n">
+      <c r="BI12" s="11" t="n">
         <v>-8.08</v>
       </c>
-      <c r="BJ12" s="14" t="n">
+      <c r="BJ12" s="11" t="n">
         <v>-33.33</v>
       </c>
-      <c r="BK12" s="14" t="n">
+      <c r="BK12" s="11" t="n">
         <v>-2.99</v>
       </c>
       <c r="BL12" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="BM12" s="14" t="n">
+      <c r="BM12" s="11" t="n">
         <v>-3.1</v>
       </c>
-      <c r="BN12" s="14" t="n">
+      <c r="BN12" s="11" t="n">
         <v>-3.34</v>
       </c>
-      <c r="BO12" s="14" t="n">
+      <c r="BO12" s="11" t="n">
         <v>-13.79</v>
       </c>
-      <c r="BP12" s="14" t="n">
+      <c r="BP12" s="11" t="n">
         <v>-30</v>
       </c>
-      <c r="BQ12" s="14" t="n">
+      <c r="BQ12" s="11" t="n">
         <v>-43.75</v>
       </c>
       <c r="BR12" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="BS12" s="16" t="n"/>
-      <c r="BT12" s="14" t="n">
+      <c r="BS12" s="12" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="BT12" s="11" t="n">
         <v>-37.5</v>
       </c>
-      <c r="BU12" s="14" t="n">
+      <c r="BU12" s="11" t="n">
         <v>-16.67</v>
       </c>
       <c r="BV12" s="10" t="n">
         <v>46.67</v>
       </c>
-      <c r="BW12" s="12" t="n">
+      <c r="BW12" s="13" t="n">
         <v>0</v>
       </c>
       <c r="BX12" s="10" t="n">
         <v>13.33</v>
       </c>
-      <c r="BY12" s="14" t="n">
-        <v>-71.43000000000001</v>
+      <c r="BY12" s="11" t="n">
+        <v>-71.43</v>
       </c>
       <c r="BZ12" s="10" t="n">
         <v>6.67</v>
       </c>
-      <c r="CA12" s="14" t="n">
+      <c r="CA12" s="11" t="n">
         <v>-45.83</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Bentel rockers__qwen3.5-4b__Bentel_iter_3</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Bentel rockers</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>Bentel_iter_3</t>
-        </is>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>100</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>2.38</v>
+        <v>6.69</v>
       </c>
       <c r="E13" s="10" t="n">
         <v>2.94</v>
@@ -2730,81 +3085,85 @@
       <c r="H13" s="10" t="n">
         <v>1.17</v>
       </c>
-      <c r="I13" s="14" t="n">
+      <c r="I13" s="11" t="n">
         <v>-1.39</v>
       </c>
       <c r="J13" s="10" t="n">
         <v>1.48</v>
       </c>
-      <c r="K13" s="14" t="n">
+      <c r="K13" s="11" t="n">
         <v>-4.2</v>
       </c>
       <c r="L13" s="10" t="n">
         <v>22.5</v>
       </c>
-      <c r="M13" s="14" t="n">
+      <c r="M13" s="11" t="n">
         <v>-10.83</v>
       </c>
-      <c r="N13" s="12" t="n">
+      <c r="N13" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O13" s="10" t="n">
         <v>20.19</v>
       </c>
-      <c r="P13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="14" t="n">
+      <c r="P13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="11" t="n">
         <v>-2</v>
       </c>
       <c r="R13" s="10" t="n">
         <v>27.77</v>
       </c>
-      <c r="S13" s="14" t="n">
+      <c r="S13" s="11" t="n">
         <v>-0.64</v>
       </c>
       <c r="T13" s="10" t="n">
         <v>19.23</v>
       </c>
-      <c r="U13" s="16" t="n"/>
+      <c r="U13" s="12" t="n">
+        <v>28</v>
+      </c>
       <c r="V13" s="10" t="n">
         <v>7.5</v>
       </c>
       <c r="W13" s="10" t="n">
         <v>14.24</v>
       </c>
-      <c r="X13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="14" t="n">
+      <c r="X13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="11" t="n">
         <v>-1.28</v>
       </c>
       <c r="Z13" s="10" t="n">
         <v>93.33</v>
       </c>
-      <c r="AA13" s="16" t="n"/>
-      <c r="AB13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="14" t="n">
+      <c r="AA13" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="11" t="n">
         <v>-5</v>
       </c>
-      <c r="AD13" s="14" t="n">
+      <c r="AD13" s="11" t="n">
         <v>-27.5</v>
       </c>
-      <c r="AE13" s="14" t="n">
+      <c r="AE13" s="11" t="n">
         <v>-11.59</v>
       </c>
-      <c r="AF13" s="12" t="n">
+      <c r="AF13" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AG13" s="10" t="n">
         <v>12.5</v>
       </c>
-      <c r="AH13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="14" t="n">
+      <c r="AH13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="11" t="n">
         <v>-4</v>
       </c>
       <c r="AJ13" s="10" t="n">
@@ -2813,25 +3172,25 @@
       <c r="AK13" s="10" t="n">
         <v>7.04</v>
       </c>
-      <c r="AL13" s="14" t="n">
+      <c r="AL13" s="11" t="n">
         <v>-3.33</v>
       </c>
       <c r="AM13" s="10" t="n">
         <v>14.49</v>
       </c>
-      <c r="AN13" s="14" t="n">
+      <c r="AN13" s="11" t="n">
         <v>-8.33</v>
       </c>
       <c r="AO13" s="10" t="n">
         <v>6.01</v>
       </c>
-      <c r="AP13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" s="14" t="n">
+      <c r="AP13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="11" t="n">
         <v>-1.19</v>
       </c>
-      <c r="AR13" s="14" t="n">
+      <c r="AR13" s="11" t="n">
         <v>-20</v>
       </c>
       <c r="AS13" s="10" t="n">
@@ -2840,20 +3199,22 @@
       <c r="AT13" s="10" t="n">
         <v>33.34</v>
       </c>
-      <c r="AU13" s="14" t="n">
+      <c r="AU13" s="11" t="n">
         <v>-5.29</v>
       </c>
-      <c r="AV13" s="14" t="n">
+      <c r="AV13" s="11" t="n">
         <v>-26.67</v>
       </c>
-      <c r="AW13" s="16" t="n"/>
+      <c r="AW13" s="15" t="n">
+        <v>-25</v>
+      </c>
       <c r="AX13" s="10" t="n">
         <v>3.33</v>
       </c>
-      <c r="AY13" s="14" t="n">
+      <c r="AY13" s="11" t="n">
         <v>-13.89</v>
       </c>
-      <c r="AZ13" s="14" t="n">
+      <c r="AZ13" s="11" t="n">
         <v>-3.33</v>
       </c>
       <c r="BA13" s="10" t="n">
@@ -2862,16 +3223,16 @@
       <c r="BB13" s="10" t="n">
         <v>3.33</v>
       </c>
-      <c r="BC13" s="14" t="n">
+      <c r="BC13" s="11" t="n">
         <v>-1.9</v>
       </c>
       <c r="BD13" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="BE13" s="14" t="n">
+      <c r="BE13" s="11" t="n">
         <v>-14.58</v>
       </c>
-      <c r="BF13" s="14" t="n">
+      <c r="BF13" s="11" t="n">
         <v>-10</v>
       </c>
       <c r="BG13" s="10" t="n">
@@ -2880,10 +3241,10 @@
       <c r="BH13" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="BI13" s="14" t="n">
+      <c r="BI13" s="11" t="n">
         <v>-8.08</v>
       </c>
-      <c r="BJ13" s="14" t="n">
+      <c r="BJ13" s="11" t="n">
         <v>-33.33</v>
       </c>
       <c r="BK13" s="10" t="n">
@@ -2895,26 +3256,28 @@
       <c r="BM13" s="10" t="n">
         <v>0.35</v>
       </c>
-      <c r="BN13" s="14" t="n">
+      <c r="BN13" s="11" t="n">
         <v>-6.67</v>
       </c>
-      <c r="BO13" s="14" t="n">
+      <c r="BO13" s="11" t="n">
         <v>-15.49</v>
       </c>
-      <c r="BP13" s="14" t="n">
+      <c r="BP13" s="11" t="n">
         <v>-20</v>
       </c>
-      <c r="BQ13" s="12" t="n">
+      <c r="BQ13" s="13" t="n">
         <v>0</v>
       </c>
       <c r="BR13" s="10" t="n">
         <v>40</v>
       </c>
-      <c r="BS13" s="16" t="n"/>
-      <c r="BT13" s="14" t="n">
+      <c r="BS13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT13" s="11" t="n">
         <v>-20.84</v>
       </c>
-      <c r="BU13" s="14" t="n">
+      <c r="BU13" s="11" t="n">
         <v>-12.5</v>
       </c>
       <c r="BV13" s="10" t="n">
@@ -2926,26 +3289,24 @@
       <c r="BX13" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="BY13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ13" s="14" t="n">
+      <c r="BY13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ13" s="11" t="n">
         <v>-6.67</v>
       </c>
       <c r="CA13" s="10" t="n">
         <v>16.67</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>llama-3.1-8b-instruct</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n"/>
-      <c r="C14" s="5" t="n"/>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
       <c r="D14" s="6" t="n">
-        <v>22.19</v>
+        <v>19.53</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>45.59</v>
@@ -3014,7 +3375,7 @@
         <v>91.67</v>
       </c>
       <c r="AA14" s="6" t="n">
-        <v>9.699999999999999</v>
+        <v>9.7</v>
       </c>
       <c r="AB14" s="6" t="n">
         <v>100</v>
@@ -3140,7 +3501,7 @@
         <v>35</v>
       </c>
       <c r="BQ14" s="6" t="n">
-        <v>73.20999999999999</v>
+        <v>73.21</v>
       </c>
       <c r="BR14" s="6" t="n">
         <v>55.56</v>
@@ -3173,16 +3534,14 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>qwen3.5-9b</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="n"/>
-      <c r="C15" s="5" t="n"/>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
       <c r="D15" s="6" t="n">
-        <v>33.28</v>
+        <v>31.91</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>53.9</v>
@@ -3209,7 +3568,7 @@
         <v>87.5</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>84.76000000000001</v>
+        <v>84.76</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>100</v>
@@ -3232,7 +3591,9 @@
       <c r="T15" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U15" s="7" t="n"/>
+      <c r="U15" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="V15" s="6" t="n">
         <v>47.5</v>
       </c>
@@ -3243,12 +3604,14 @@
         <v>100</v>
       </c>
       <c r="Y15" s="6" t="n">
-        <v>73.98999999999999</v>
+        <v>73.99</v>
       </c>
       <c r="Z15" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="AA15" s="7" t="n"/>
+      <c r="AA15" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="AB15" s="6" t="n">
         <v>100</v>
       </c>
@@ -3259,7 +3622,7 @@
         <v>82.5</v>
       </c>
       <c r="AE15" s="6" t="n">
-        <v>91.79000000000001</v>
+        <v>91.79</v>
       </c>
       <c r="AF15" s="6" t="n">
         <v>100</v>
@@ -3406,112 +3769,110 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>BSU-SLIM__Qwen3.5-9B-Base__playpen-prm-9b-best_of_n</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>BSU-SLIM</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>prm-search-best_of_n</t>
-        </is>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>105</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="E16" s="14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E16" s="11" t="n">
         <v>-3.98</v>
       </c>
-      <c r="F16" s="14" t="n">
+      <c r="F16" s="11" t="n">
         <v>-1.48</v>
       </c>
       <c r="G16" s="10" t="n">
         <v>22.03</v>
       </c>
-      <c r="H16" s="14" t="n">
+      <c r="H16" s="11" t="n">
         <v>-15.94</v>
       </c>
-      <c r="I16" s="14" t="n">
+      <c r="I16" s="11" t="n">
         <v>-9.73</v>
       </c>
       <c r="J16" s="10" t="n">
         <v>4.23</v>
       </c>
-      <c r="K16" s="14" t="n">
+      <c r="K16" s="11" t="n">
         <v>-19.55</v>
       </c>
-      <c r="L16" s="14" t="n">
+      <c r="L16" s="11" t="n">
         <v>-42.5</v>
       </c>
-      <c r="M16" s="14" t="n">
+      <c r="M16" s="11" t="n">
         <v>-27.35</v>
       </c>
-      <c r="N16" s="12" t="n">
+      <c r="N16" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O16" s="10" t="n">
         <v>1.92</v>
       </c>
-      <c r="P16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="14" t="n">
+      <c r="P16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="11" t="n">
         <v>-4</v>
       </c>
       <c r="R16" s="10" t="n">
         <v>22.22</v>
       </c>
-      <c r="S16" s="14" t="n">
+      <c r="S16" s="11" t="n">
         <v>-0.12</v>
       </c>
       <c r="T16" s="10" t="n">
         <v>33.08</v>
       </c>
-      <c r="U16" s="16" t="n"/>
+      <c r="U16" s="12" t="n">
+        <v>13.95</v>
+      </c>
       <c r="V16" s="10" t="n">
         <v>52.5</v>
       </c>
-      <c r="W16" s="14" t="n">
+      <c r="W16" s="11" t="n">
         <v>-28.61</v>
       </c>
-      <c r="X16" s="14" t="n">
+      <c r="X16" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="Y16" s="14" t="n">
+      <c r="Y16" s="11" t="n">
         <v>-5.59</v>
       </c>
       <c r="Z16" s="10" t="n">
         <v>96.67</v>
       </c>
-      <c r="AA16" s="16" t="n"/>
-      <c r="AB16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="14" t="n">
+      <c r="AA16" s="12" t="n">
+        <v>43.68</v>
+      </c>
+      <c r="AB16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="11" t="n">
         <v>-7</v>
       </c>
       <c r="AD16" s="10" t="n">
         <v>17.5</v>
       </c>
-      <c r="AE16" s="14" t="n">
+      <c r="AE16" s="11" t="n">
         <v>-28.41</v>
       </c>
-      <c r="AF16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" s="14" t="n">
+      <c r="AF16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="11" t="n">
         <v>-20</v>
       </c>
-      <c r="AH16" s="14" t="n">
+      <c r="AH16" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="AI16" s="14" t="n">
+      <c r="AI16" s="11" t="n">
         <v>-1.57</v>
       </c>
       <c r="AJ16" s="10" t="n">
@@ -3520,13 +3881,13 @@
       <c r="AK16" s="10" t="n">
         <v>4.23</v>
       </c>
-      <c r="AL16" s="14" t="n">
+      <c r="AL16" s="11" t="n">
         <v>-2.22</v>
       </c>
-      <c r="AM16" s="14" t="n">
+      <c r="AM16" s="11" t="n">
         <v>-13.16</v>
       </c>
-      <c r="AN16" s="12" t="n">
+      <c r="AN16" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AO16" s="10" t="n">
@@ -3538,7 +3899,7 @@
       <c r="AQ16" s="10" t="n">
         <v>2.36</v>
       </c>
-      <c r="AR16" s="14" t="n">
+      <c r="AR16" s="11" t="n">
         <v>-20</v>
       </c>
       <c r="AS16" s="10" t="n">
@@ -3547,120 +3908,120 @@
       <c r="AT16" s="10" t="n">
         <v>3.34</v>
       </c>
-      <c r="AU16" s="14" t="n">
+      <c r="AU16" s="11" t="n">
         <v>-13.04</v>
       </c>
       <c r="AV16" s="10" t="n">
         <v>86.67</v>
       </c>
-      <c r="AW16" s="14" t="n">
+      <c r="AW16" s="11" t="n">
         <v>-9.17</v>
       </c>
       <c r="AX16" s="10" t="n">
         <v>83.33</v>
       </c>
-      <c r="AY16" s="14" t="n">
+      <c r="AY16" s="11" t="n">
         <v>-64.61</v>
       </c>
       <c r="AZ16" s="10" t="n">
         <v>80</v>
       </c>
-      <c r="BA16" s="14" t="n">
-        <v>-81.26000000000001</v>
+      <c r="BA16" s="11" t="n">
+        <v>-81.26</v>
       </c>
       <c r="BB16" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="BC16" s="14" t="n">
+      <c r="BC16" s="11" t="n">
         <v>-10.15</v>
       </c>
-      <c r="BD16" s="14" t="n">
+      <c r="BD16" s="11" t="n">
         <v>-53.33</v>
       </c>
-      <c r="BE16" s="16" t="n"/>
-      <c r="BF16" s="14" t="n">
+      <c r="BE16" s="15" t="n">
+        <v>-40.62</v>
+      </c>
+      <c r="BF16" s="11" t="n">
         <v>-30</v>
       </c>
-      <c r="BG16" s="16" t="n"/>
+      <c r="BG16" s="15" t="n">
+        <v>-35.56</v>
+      </c>
       <c r="BH16" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="BI16" s="14" t="n">
+      <c r="BI16" s="11" t="n">
         <v>-12.47</v>
       </c>
-      <c r="BJ16" s="14" t="n">
+      <c r="BJ16" s="11" t="n">
         <v>-16.67</v>
       </c>
-      <c r="BK16" s="14" t="n">
+      <c r="BK16" s="11" t="n">
         <v>-7.44</v>
       </c>
-      <c r="BL16" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM16" s="14" t="n">
+      <c r="BL16" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" s="11" t="n">
         <v>-8</v>
       </c>
-      <c r="BN16" s="14" t="n">
+      <c r="BN16" s="11" t="n">
         <v>-16.67</v>
       </c>
       <c r="BO16" s="10" t="n">
         <v>26.75</v>
       </c>
-      <c r="BP16" s="14" t="n">
+      <c r="BP16" s="11" t="n">
         <v>-50</v>
       </c>
-      <c r="BQ16" s="14" t="n">
+      <c r="BQ16" s="11" t="n">
         <v>-75</v>
       </c>
-      <c r="BR16" s="14" t="n">
+      <c r="BR16" s="11" t="n">
         <v>-10</v>
       </c>
-      <c r="BS16" s="16" t="n"/>
-      <c r="BT16" s="14" t="n">
+      <c r="BS16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT16" s="11" t="n">
         <v>-25</v>
       </c>
-      <c r="BU16" s="14" t="n">
+      <c r="BU16" s="11" t="n">
         <v>-4.17</v>
       </c>
       <c r="BV16" s="10" t="n">
         <v>83.33</v>
       </c>
-      <c r="BW16" s="14" t="n">
+      <c r="BW16" s="11" t="n">
         <v>-33.33</v>
       </c>
       <c r="BX16" s="10" t="n">
         <v>76.67</v>
       </c>
-      <c r="BY16" s="14" t="n">
+      <c r="BY16" s="11" t="n">
         <v>-53.33</v>
       </c>
       <c r="BZ16" s="10" t="n">
         <v>76.67</v>
       </c>
-      <c r="CA16" s="14" t="n">
+      <c r="CA16" s="11" t="n">
         <v>-77.33</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>Dialogue Architects__qwen3.5-9b__SCoRe_Qwen3.5-9B</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Dialogue Architects</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>SCoRe_Qwen3.5-9B</t>
-        </is>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>108</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="E17" s="14" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="E17" s="11" t="n">
         <v>-0.64</v>
       </c>
       <c r="F17" s="10" t="n">
@@ -3672,28 +4033,28 @@
       <c r="H17" s="10" t="n">
         <v>0.58</v>
       </c>
-      <c r="I17" s="14" t="n">
+      <c r="I17" s="11" t="n">
         <v>-1.54</v>
       </c>
-      <c r="J17" s="14" t="n">
+      <c r="J17" s="11" t="n">
         <v>-2.38</v>
       </c>
-      <c r="K17" s="14" t="n">
+      <c r="K17" s="11" t="n">
         <v>-0.87</v>
       </c>
-      <c r="L17" s="14" t="n">
+      <c r="L17" s="11" t="n">
         <v>-10</v>
       </c>
-      <c r="M17" s="14" t="n">
+      <c r="M17" s="11" t="n">
         <v>-0.89</v>
       </c>
-      <c r="N17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="12" t="n">
+      <c r="N17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="13" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="10" t="n">
@@ -3702,66 +4063,70 @@
       <c r="R17" s="10" t="n">
         <v>5.55</v>
       </c>
-      <c r="S17" s="14" t="n">
+      <c r="S17" s="11" t="n">
         <v>-3.06</v>
       </c>
-      <c r="T17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" s="16" t="n"/>
+      <c r="T17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="V17" s="10" t="n">
         <v>22.5</v>
       </c>
-      <c r="W17" s="14" t="n">
+      <c r="W17" s="11" t="n">
         <v>-8.33</v>
       </c>
-      <c r="X17" s="12" t="n">
+      <c r="X17" s="13" t="n">
         <v>0</v>
       </c>
       <c r="Y17" s="10" t="n">
         <v>0.51</v>
       </c>
-      <c r="Z17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="16" t="n"/>
-      <c r="AB17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="14" t="n">
+      <c r="Z17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="11" t="n">
         <v>-2</v>
       </c>
-      <c r="AD17" s="14" t="n">
+      <c r="AD17" s="11" t="n">
         <v>-2.5</v>
       </c>
-      <c r="AE17" s="14" t="n">
+      <c r="AE17" s="11" t="n">
         <v>-1.2</v>
       </c>
-      <c r="AF17" s="12" t="n">
+      <c r="AF17" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AG17" s="10" t="n">
         <v>2.5</v>
       </c>
-      <c r="AH17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" s="12" t="n">
+      <c r="AH17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>0.88</v>
       </c>
-      <c r="AL17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN17" s="12" t="n">
+      <c r="AL17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AO17" s="10" t="n">
@@ -3773,7 +4138,7 @@
       <c r="AQ17" s="10" t="n">
         <v>3.59</v>
       </c>
-      <c r="AR17" s="12" t="n">
+      <c r="AR17" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AS17" s="10" t="n">
@@ -3782,7 +4147,7 @@
       <c r="AT17" s="10" t="n">
         <v>6.67</v>
       </c>
-      <c r="AU17" s="12" t="n">
+      <c r="AU17" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AV17" s="10" t="n">
@@ -3791,19 +4156,19 @@
       <c r="AW17" s="10" t="n">
         <v>30.36</v>
       </c>
-      <c r="AX17" s="14" t="n">
+      <c r="AX17" s="11" t="n">
         <v>-3.34</v>
       </c>
-      <c r="AY17" s="14" t="n">
+      <c r="AY17" s="11" t="n">
         <v>-2.5</v>
       </c>
       <c r="AZ17" s="10" t="n">
         <v>3.33</v>
       </c>
-      <c r="BA17" s="14" t="n">
+      <c r="BA17" s="11" t="n">
         <v>-19.17</v>
       </c>
-      <c r="BB17" s="14" t="n">
+      <c r="BB17" s="11" t="n">
         <v>-1.67</v>
       </c>
       <c r="BC17" s="10" t="n">
@@ -3812,43 +4177,43 @@
       <c r="BD17" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="BE17" s="14" t="n">
+      <c r="BE17" s="11" t="n">
         <v>-8</v>
       </c>
-      <c r="BF17" s="14" t="n">
+      <c r="BF17" s="11" t="n">
         <v>-3.33</v>
       </c>
-      <c r="BG17" s="14" t="n">
+      <c r="BG17" s="11" t="n">
         <v>-25.56</v>
       </c>
-      <c r="BH17" s="14" t="n">
+      <c r="BH17" s="11" t="n">
         <v>-2.5</v>
       </c>
-      <c r="BI17" s="14" t="n">
+      <c r="BI17" s="11" t="n">
         <v>-1.93</v>
       </c>
-      <c r="BJ17" s="14" t="n">
+      <c r="BJ17" s="11" t="n">
         <v>-16.67</v>
       </c>
-      <c r="BK17" s="14" t="n">
+      <c r="BK17" s="11" t="n">
         <v>-12.17</v>
       </c>
-      <c r="BL17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM17" s="14" t="n">
+      <c r="BL17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM17" s="11" t="n">
         <v>-7</v>
       </c>
-      <c r="BN17" s="12" t="n">
+      <c r="BN17" s="13" t="n">
         <v>0</v>
       </c>
       <c r="BO17" s="10" t="n">
         <v>2.22</v>
       </c>
-      <c r="BP17" s="14" t="n">
+      <c r="BP17" s="11" t="n">
         <v>-30</v>
       </c>
-      <c r="BQ17" s="14" t="n">
+      <c r="BQ17" s="11" t="n">
         <v>-12.5</v>
       </c>
       <c r="BR17" s="10" t="n">
@@ -3857,49 +4222,43 @@
       <c r="BS17" s="10" t="n">
         <v>80</v>
       </c>
-      <c r="BT17" s="14" t="n">
+      <c r="BT17" s="11" t="n">
         <v>-33.33</v>
       </c>
-      <c r="BU17" s="14" t="n">
+      <c r="BU17" s="11" t="n">
         <v>-4.17</v>
       </c>
       <c r="BV17" s="10" t="n">
         <v>6.67</v>
       </c>
-      <c r="BW17" s="14" t="n">
+      <c r="BW17" s="11" t="n">
         <v>-23.33</v>
       </c>
-      <c r="BX17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA17" s="12" t="n">
+      <c r="BX17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ17" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA17" s="13" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>LLP: Large Language Problems__qwen3.5-9b__llp-final</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>LLP: Large Language Problems</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>llp-final</t>
-        </is>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>111</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>21.33</v>
+        <v>21.48</v>
       </c>
       <c r="E18" s="10" t="n">
         <v>3.9</v>
@@ -3913,13 +4272,13 @@
       <c r="H18" s="10" t="n">
         <v>7.26</v>
       </c>
-      <c r="I18" s="14" t="n">
+      <c r="I18" s="11" t="n">
         <v>-2.82</v>
       </c>
       <c r="J18" s="10" t="n">
         <v>4.48</v>
       </c>
-      <c r="K18" s="14" t="n">
+      <c r="K18" s="11" t="n">
         <v>-8.1</v>
       </c>
       <c r="L18" s="10" t="n">
@@ -3928,13 +4287,13 @@
       <c r="M18" s="10" t="n">
         <v>5.24</v>
       </c>
-      <c r="N18" s="12" t="n">
+      <c r="N18" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="10" t="n">
         <v>33.65</v>
       </c>
-      <c r="P18" s="12" t="n">
+      <c r="P18" s="13" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="10" t="n">
@@ -3943,20 +4302,22 @@
       <c r="R18" s="10" t="n">
         <v>5.55</v>
       </c>
-      <c r="S18" s="14" t="n">
+      <c r="S18" s="11" t="n">
         <v>-13.06</v>
       </c>
       <c r="T18" s="10" t="n">
         <v>70.77</v>
       </c>
-      <c r="U18" s="16" t="n"/>
+      <c r="U18" s="12" t="n">
+        <v>43.48</v>
+      </c>
       <c r="V18" s="10" t="n">
         <v>52.5</v>
       </c>
-      <c r="W18" s="14" t="n">
+      <c r="W18" s="11" t="n">
         <v>-0.26</v>
       </c>
-      <c r="X18" s="14" t="n">
+      <c r="X18" s="11" t="n">
         <v>-1</v>
       </c>
       <c r="Y18" s="10" t="n">
@@ -3965,11 +4326,13 @@
       <c r="Z18" s="10" t="n">
         <v>98.33</v>
       </c>
-      <c r="AA18" s="16" t="n"/>
-      <c r="AB18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" s="14" t="n">
+      <c r="AA18" s="12" t="n">
+        <v>18.64</v>
+      </c>
+      <c r="AB18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="11" t="n">
         <v>-14</v>
       </c>
       <c r="AD18" s="10" t="n">
@@ -3978,16 +4341,16 @@
       <c r="AE18" s="10" t="n">
         <v>7.06</v>
       </c>
-      <c r="AF18" s="12" t="n">
+      <c r="AF18" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AG18" s="10" t="n">
         <v>17.5</v>
       </c>
-      <c r="AH18" s="14" t="n">
+      <c r="AH18" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="AI18" s="14" t="n">
+      <c r="AI18" s="11" t="n">
         <v>-1.57</v>
       </c>
       <c r="AJ18" s="10" t="n">
@@ -3996,13 +4359,13 @@
       <c r="AK18" s="10" t="n">
         <v>33.38</v>
       </c>
-      <c r="AL18" s="12" t="n">
+      <c r="AL18" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AM18" s="10" t="n">
         <v>16.67</v>
       </c>
-      <c r="AN18" s="12" t="n">
+      <c r="AN18" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AO18" s="10" t="n">
@@ -4023,7 +4386,7 @@
       <c r="AT18" s="10" t="n">
         <v>26.67</v>
       </c>
-      <c r="AU18" s="12" t="n">
+      <c r="AU18" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AV18" s="10" t="n">
@@ -4035,100 +4398,102 @@
       <c r="AX18" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="AY18" s="14" t="n">
+      <c r="AY18" s="11" t="n">
         <v>-3.64</v>
       </c>
       <c r="AZ18" s="10" t="n">
         <v>23.33</v>
       </c>
-      <c r="BA18" s="14" t="n">
+      <c r="BA18" s="11" t="n">
         <v>-8.75</v>
       </c>
       <c r="BB18" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="BC18" s="14" t="n">
+      <c r="BC18" s="11" t="n">
         <v>-6.59</v>
       </c>
-      <c r="BD18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE18" s="14" t="n">
+      <c r="BD18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" s="11" t="n">
         <v>-14.49</v>
       </c>
       <c r="BF18" s="10" t="n">
         <v>63.33</v>
       </c>
-      <c r="BG18" s="14" t="n">
+      <c r="BG18" s="11" t="n">
         <v>-30.92</v>
       </c>
       <c r="BH18" s="10" t="n">
         <v>12.5</v>
       </c>
-      <c r="BI18" s="14" t="n">
+      <c r="BI18" s="11" t="n">
         <v>-15.1</v>
       </c>
-      <c r="BJ18" s="14" t="n">
+      <c r="BJ18" s="11" t="n">
         <v>-100</v>
       </c>
-      <c r="BK18" s="16" t="n"/>
-      <c r="BL18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM18" s="14" t="n">
+      <c r="BK18" s="15" t="n">
+        <v>-28.54</v>
+      </c>
+      <c r="BL18" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM18" s="11" t="n">
         <v>-6.67</v>
       </c>
-      <c r="BN18" s="14" t="n">
+      <c r="BN18" s="11" t="n">
         <v>-6.67</v>
       </c>
-      <c r="BO18" s="14" t="n">
+      <c r="BO18" s="11" t="n">
         <v>-2.14</v>
       </c>
-      <c r="BP18" s="14" t="n">
+      <c r="BP18" s="11" t="n">
         <v>-60</v>
       </c>
-      <c r="BQ18" s="16" t="n"/>
+      <c r="BQ18" s="15" t="n">
+        <v>-100</v>
+      </c>
       <c r="BR18" s="10" t="n">
         <v>10</v>
       </c>
       <c r="BS18" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="BT18" s="14" t="n">
+      <c r="BT18" s="11" t="n">
         <v>-12.5</v>
       </c>
-      <c r="BU18" s="14" t="n">
+      <c r="BU18" s="11" t="n">
         <v>-4.17</v>
       </c>
       <c r="BV18" s="10" t="n">
         <v>26.67</v>
       </c>
-      <c r="BW18" s="14" t="n">
-        <v>-8.779999999999999</v>
+      <c r="BW18" s="11" t="n">
+        <v>-8.78</v>
       </c>
       <c r="BX18" s="10" t="n">
         <v>66.67</v>
       </c>
-      <c r="BY18" s="14" t="n">
+      <c r="BY18" s="11" t="n">
         <v>-7.41</v>
       </c>
       <c r="BZ18" s="10" t="n">
         <v>53.34</v>
       </c>
-      <c r="CA18" s="14" t="n">
+      <c r="CA18" s="11" t="n">
         <v>-4.35</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>qwen3.5-27b</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
       <c r="D19" s="6" t="n">
-        <v>62.34</v>
+        <v>60.3</v>
       </c>
       <c r="E19" s="6" t="n">
         <v>65.05</v>
@@ -4146,7 +4511,7 @@
         <v>43.51</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>68.01000000000001</v>
+        <v>68.01</v>
       </c>
       <c r="K19" s="6" t="n">
         <v>63.98</v>
@@ -4287,7 +4652,7 @@
         <v>86.67</v>
       </c>
       <c r="BE19" s="6" t="n">
-        <v>85.45999999999999</v>
+        <v>85.46</v>
       </c>
       <c r="BF19" s="6" t="n">
         <v>50</v>
@@ -4356,68 +4721,62 @@
         <v>95</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>SLED-BSU__Qwen3.5-27B-sft-ep1__prm-ep1-best_of_n</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>SLED-BSU</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>prm-guided-best_of_n</t>
-        </is>
-      </c>
-      <c r="D20" s="14" t="n">
-        <v>-15.44</v>
-      </c>
-      <c r="E20" s="14" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>-13.4</v>
+      </c>
+      <c r="E20" s="11" t="n">
         <v>-1.25</v>
       </c>
-      <c r="F20" s="14" t="n">
+      <c r="F20" s="11" t="n">
         <v>-7.98</v>
       </c>
-      <c r="G20" s="14" t="n">
+      <c r="G20" s="11" t="n">
         <v>-1.17</v>
       </c>
-      <c r="H20" s="14" t="n">
+      <c r="H20" s="11" t="n">
         <v>-7.92</v>
       </c>
-      <c r="I20" s="14" t="n">
+      <c r="I20" s="11" t="n">
         <v>-13.49</v>
       </c>
-      <c r="J20" s="14" t="n">
+      <c r="J20" s="11" t="n">
         <v>-0.13</v>
       </c>
-      <c r="K20" s="14" t="n">
+      <c r="K20" s="11" t="n">
         <v>-19.75</v>
       </c>
-      <c r="L20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="14" t="n">
+      <c r="L20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="11" t="n">
         <v>-42.5</v>
       </c>
-      <c r="N20" s="12" t="n">
+      <c r="N20" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O20" s="10" t="n">
         <v>14.42</v>
       </c>
-      <c r="P20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="14" t="n">
+      <c r="P20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="R20" s="14" t="n">
+      <c r="R20" s="11" t="n">
         <v>-61.11</v>
       </c>
-      <c r="S20" s="14" t="n">
+      <c r="S20" s="11" t="n">
         <v>-56.5</v>
       </c>
       <c r="T20" s="10" t="n">
@@ -4426,170 +4785,172 @@
       <c r="U20" s="10" t="n">
         <v>1.05</v>
       </c>
-      <c r="V20" s="12" t="n">
+      <c r="V20" s="13" t="n">
         <v>0</v>
       </c>
       <c r="W20" s="10" t="n">
         <v>38.05</v>
       </c>
-      <c r="X20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="14" t="n">
+      <c r="X20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="11" t="n">
         <v>-4.14</v>
       </c>
-      <c r="Z20" s="14" t="n">
+      <c r="Z20" s="11" t="n">
         <v>-1.66</v>
       </c>
-      <c r="AA20" s="14" t="n">
+      <c r="AA20" s="11" t="n">
         <v>-7.51</v>
       </c>
-      <c r="AB20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="14" t="n">
+      <c r="AB20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="11" t="n">
         <v>-1</v>
       </c>
-      <c r="AD20" s="12" t="n">
+      <c r="AD20" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AE20" s="10" t="n">
         <v>4.32</v>
       </c>
-      <c r="AF20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" s="14" t="n">
+      <c r="AF20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="11" t="n">
         <v>-2.5</v>
       </c>
-      <c r="AH20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" s="14" t="n">
+      <c r="AH20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="11" t="n">
         <v>-4</v>
       </c>
-      <c r="AJ20" s="12" t="n">
+      <c r="AJ20" s="13" t="n">
         <v>0</v>
       </c>
       <c r="AK20" s="10" t="n">
         <v>23.42</v>
       </c>
-      <c r="AL20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" s="14" t="n">
+      <c r="AL20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="11" t="n">
         <v>-10</v>
       </c>
       <c r="AN20" s="10" t="n">
         <v>3.33</v>
       </c>
-      <c r="AO20" s="14" t="n">
+      <c r="AO20" s="11" t="n">
         <v>-3.39</v>
       </c>
-      <c r="AP20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" s="14" t="n">
+      <c r="AP20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" s="11" t="n">
         <v>-28.45</v>
       </c>
-      <c r="AR20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" s="14" t="n">
+      <c r="AR20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" s="11" t="n">
         <v>-3.61</v>
       </c>
       <c r="AT20" s="10" t="n">
         <v>3.33</v>
       </c>
-      <c r="AU20" s="14" t="n">
+      <c r="AU20" s="11" t="n">
         <v>-40</v>
       </c>
       <c r="AV20" s="10" t="n">
         <v>33.33</v>
       </c>
-      <c r="AW20" s="14" t="n">
+      <c r="AW20" s="11" t="n">
         <v>-5.2</v>
       </c>
-      <c r="AX20" s="14" t="n">
+      <c r="AX20" s="11" t="n">
         <v>-13.34</v>
       </c>
-      <c r="AY20" s="14" t="n">
+      <c r="AY20" s="11" t="n">
         <v>-6.67</v>
       </c>
-      <c r="AZ20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" s="14" t="n">
+      <c r="AZ20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" s="11" t="n">
         <v>-31.11</v>
       </c>
       <c r="BB20" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="BC20" s="14" t="n">
+      <c r="BC20" s="11" t="n">
         <v>-28.28</v>
       </c>
-      <c r="BD20" s="14" t="n">
+      <c r="BD20" s="11" t="n">
         <v>-13.34</v>
       </c>
-      <c r="BE20" s="14" t="n">
+      <c r="BE20" s="11" t="n">
         <v>-28.73</v>
       </c>
       <c r="BF20" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="BG20" s="14" t="n">
+      <c r="BG20" s="11" t="n">
         <v>-50</v>
       </c>
       <c r="BH20" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="BI20" s="14" t="n">
+      <c r="BI20" s="11" t="n">
         <v>-6.83</v>
       </c>
-      <c r="BJ20" s="14" t="n">
+      <c r="BJ20" s="11" t="n">
         <v>-66.67</v>
       </c>
-      <c r="BK20" s="14" t="n">
+      <c r="BK20" s="11" t="n">
         <v>-25.94</v>
       </c>
-      <c r="BL20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM20" s="14" t="n">
+      <c r="BL20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM20" s="11" t="n">
         <v>-11</v>
       </c>
-      <c r="BN20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO20" s="14" t="n">
+      <c r="BN20" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO20" s="11" t="n">
         <v>-7.77</v>
       </c>
-      <c r="BP20" s="14" t="n">
+      <c r="BP20" s="11" t="n">
         <v>-40</v>
       </c>
-      <c r="BQ20" s="14" t="n">
+      <c r="BQ20" s="11" t="n">
         <v>-22.03</v>
       </c>
-      <c r="BR20" s="14" t="n">
+      <c r="BR20" s="11" t="n">
         <v>-50</v>
       </c>
-      <c r="BS20" s="16" t="n"/>
-      <c r="BT20" s="14" t="n">
+      <c r="BS20" s="15" t="n">
+        <v>-80</v>
+      </c>
+      <c r="BT20" s="11" t="n">
         <v>-16.67</v>
       </c>
-      <c r="BU20" s="14" t="n">
+      <c r="BU20" s="11" t="n">
         <v>-20.84</v>
       </c>
       <c r="BV20" s="10" t="n">
         <v>66.67</v>
       </c>
-      <c r="BW20" s="14" t="n">
+      <c r="BW20" s="11" t="n">
         <v>-12.03</v>
       </c>
       <c r="BX20" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="BY20" s="14" t="n">
+      <c r="BY20" s="11" t="n">
         <v>-8.18</v>
       </c>
       <c r="BZ20" s="10" t="n">
@@ -4599,1004 +4960,1009 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1" s="15"/>
-    <row r="22" ht="15.75" customHeight="1" s="15"/>
-    <row r="23" ht="15.75" customHeight="1" s="15"/>
-    <row r="24" ht="15.75" customHeight="1" s="15"/>
-    <row r="25" ht="15.75" customHeight="1" s="15"/>
-    <row r="26" ht="15.75" customHeight="1" s="15"/>
-    <row r="27" ht="15.75" customHeight="1" s="15"/>
-    <row r="28" ht="15.75" customHeight="1" s="15"/>
-    <row r="29" ht="15.75" customHeight="1" s="15"/>
-    <row r="30" ht="15.75" customHeight="1" s="15"/>
-    <row r="31" ht="15.75" customHeight="1" s="15"/>
-    <row r="32" ht="15.75" customHeight="1" s="15"/>
-    <row r="33" ht="15.75" customHeight="1" s="15"/>
-    <row r="34" ht="15.75" customHeight="1" s="15"/>
-    <row r="35" ht="15.75" customHeight="1" s="15"/>
-    <row r="36" ht="15.75" customHeight="1" s="15"/>
-    <row r="37" ht="15.75" customHeight="1" s="15"/>
-    <row r="38" ht="15.75" customHeight="1" s="15"/>
-    <row r="39" ht="15.75" customHeight="1" s="15"/>
-    <row r="40" ht="15.75" customHeight="1" s="15"/>
-    <row r="41" ht="15.75" customHeight="1" s="15"/>
-    <row r="42" ht="15.75" customHeight="1" s="15"/>
-    <row r="43" ht="15.75" customHeight="1" s="15"/>
-    <row r="44" ht="15.75" customHeight="1" s="15"/>
-    <row r="45" ht="15.75" customHeight="1" s="15"/>
-    <row r="46" ht="15.75" customHeight="1" s="15"/>
-    <row r="47" ht="15.75" customHeight="1" s="15"/>
-    <row r="48" ht="15.75" customHeight="1" s="15"/>
-    <row r="49" ht="15.75" customHeight="1" s="15"/>
-    <row r="50" ht="15.75" customHeight="1" s="15"/>
-    <row r="51" ht="15.75" customHeight="1" s="15"/>
-    <row r="52" ht="15.75" customHeight="1" s="15"/>
-    <row r="53" ht="15.75" customHeight="1" s="15"/>
-    <row r="54" ht="15.75" customHeight="1" s="15"/>
-    <row r="55" ht="15.75" customHeight="1" s="15"/>
-    <row r="56" ht="15.75" customHeight="1" s="15"/>
-    <row r="57" ht="15.75" customHeight="1" s="15"/>
-    <row r="58" ht="15.75" customHeight="1" s="15"/>
-    <row r="59" ht="15.75" customHeight="1" s="15"/>
-    <row r="60" ht="15.75" customHeight="1" s="15"/>
-    <row r="61" ht="15.75" customHeight="1" s="15"/>
-    <row r="62" ht="15.75" customHeight="1" s="15"/>
-    <row r="63" ht="15.75" customHeight="1" s="15"/>
-    <row r="64" ht="15.75" customHeight="1" s="15"/>
-    <row r="65" ht="15.75" customHeight="1" s="15"/>
-    <row r="66" ht="15.75" customHeight="1" s="15"/>
-    <row r="67" ht="15.75" customHeight="1" s="15"/>
-    <row r="68" ht="15.75" customHeight="1" s="15"/>
-    <row r="69" ht="15.75" customHeight="1" s="15"/>
-    <row r="70" ht="15.75" customHeight="1" s="15"/>
-    <row r="71" ht="15.75" customHeight="1" s="15"/>
-    <row r="72" ht="15.75" customHeight="1" s="15"/>
-    <row r="73" ht="15.75" customHeight="1" s="15"/>
-    <row r="74" ht="15.75" customHeight="1" s="15"/>
-    <row r="75" ht="15.75" customHeight="1" s="15"/>
-    <row r="76" ht="15.75" customHeight="1" s="15"/>
-    <row r="77" ht="15.75" customHeight="1" s="15"/>
-    <row r="78" ht="15.75" customHeight="1" s="15"/>
-    <row r="79" ht="15.75" customHeight="1" s="15"/>
-    <row r="80" ht="15.75" customHeight="1" s="15"/>
-    <row r="81" ht="15.75" customHeight="1" s="15"/>
-    <row r="82" ht="15.75" customHeight="1" s="15"/>
-    <row r="83" ht="15.75" customHeight="1" s="15"/>
-    <row r="84" ht="15.75" customHeight="1" s="15"/>
-    <row r="85" ht="15.75" customHeight="1" s="15"/>
-    <row r="86" ht="15.75" customHeight="1" s="15"/>
-    <row r="87" ht="15.75" customHeight="1" s="15"/>
-    <row r="88" ht="15.75" customHeight="1" s="15"/>
-    <row r="89" ht="15.75" customHeight="1" s="15"/>
-    <row r="90" ht="15.75" customHeight="1" s="15"/>
-    <row r="91" ht="15.75" customHeight="1" s="15"/>
-    <row r="92" ht="15.75" customHeight="1" s="15"/>
-    <row r="93" ht="15.75" customHeight="1" s="15"/>
-    <row r="94" ht="15.75" customHeight="1" s="15"/>
-    <row r="95" ht="15.75" customHeight="1" s="15"/>
-    <row r="96" ht="15.75" customHeight="1" s="15"/>
-    <row r="97" ht="15.75" customHeight="1" s="15"/>
-    <row r="98" ht="15.75" customHeight="1" s="15"/>
-    <row r="99" ht="15.75" customHeight="1" s="15"/>
-    <row r="100" ht="15.75" customHeight="1" s="15"/>
-    <row r="101" ht="15.75" customHeight="1" s="15"/>
-    <row r="102" ht="15.75" customHeight="1" s="15"/>
-    <row r="103" ht="15.75" customHeight="1" s="15"/>
-    <row r="104" ht="15.75" customHeight="1" s="15"/>
-    <row r="105" ht="15.75" customHeight="1" s="15"/>
-    <row r="106" ht="15.75" customHeight="1" s="15"/>
-    <row r="107" ht="15.75" customHeight="1" s="15"/>
-    <row r="108" ht="15.75" customHeight="1" s="15"/>
-    <row r="109" ht="15.75" customHeight="1" s="15"/>
-    <row r="110" ht="15.75" customHeight="1" s="15"/>
-    <row r="111" ht="15.75" customHeight="1" s="15"/>
-    <row r="112" ht="15.75" customHeight="1" s="15"/>
-    <row r="113" ht="15.75" customHeight="1" s="15"/>
-    <row r="114" ht="15.75" customHeight="1" s="15"/>
-    <row r="115" ht="15.75" customHeight="1" s="15"/>
-    <row r="116" ht="15.75" customHeight="1" s="15"/>
-    <row r="117" ht="15.75" customHeight="1" s="15"/>
-    <row r="118" ht="15.75" customHeight="1" s="15"/>
-    <row r="119" ht="15.75" customHeight="1" s="15"/>
-    <row r="120" ht="15.75" customHeight="1" s="15"/>
-    <row r="121" ht="15.75" customHeight="1" s="15"/>
-    <row r="122" ht="15.75" customHeight="1" s="15"/>
-    <row r="123" ht="15.75" customHeight="1" s="15"/>
-    <row r="124" ht="15.75" customHeight="1" s="15"/>
-    <row r="125" ht="15.75" customHeight="1" s="15"/>
-    <row r="126" ht="15.75" customHeight="1" s="15"/>
-    <row r="127" ht="15.75" customHeight="1" s="15"/>
-    <row r="128" ht="15.75" customHeight="1" s="15"/>
-    <row r="129" ht="15.75" customHeight="1" s="15"/>
-    <row r="130" ht="15.75" customHeight="1" s="15"/>
-    <row r="131" ht="15.75" customHeight="1" s="15"/>
-    <row r="132" ht="15.75" customHeight="1" s="15"/>
-    <row r="133" ht="15.75" customHeight="1" s="15"/>
-    <row r="134" ht="15.75" customHeight="1" s="15"/>
-    <row r="135" ht="15.75" customHeight="1" s="15"/>
-    <row r="136" ht="15.75" customHeight="1" s="15"/>
-    <row r="137" ht="15.75" customHeight="1" s="15"/>
-    <row r="138" ht="15.75" customHeight="1" s="15"/>
-    <row r="139" ht="15.75" customHeight="1" s="15"/>
-    <row r="140" ht="15.75" customHeight="1" s="15"/>
-    <row r="141" ht="15.75" customHeight="1" s="15"/>
-    <row r="142" ht="15.75" customHeight="1" s="15"/>
-    <row r="143" ht="15.75" customHeight="1" s="15"/>
-    <row r="144" ht="15.75" customHeight="1" s="15"/>
-    <row r="145" ht="15.75" customHeight="1" s="15"/>
-    <row r="146" ht="15.75" customHeight="1" s="15"/>
-    <row r="147" ht="15.75" customHeight="1" s="15"/>
-    <row r="148" ht="15.75" customHeight="1" s="15"/>
-    <row r="149" ht="15.75" customHeight="1" s="15"/>
-    <row r="150" ht="15.75" customHeight="1" s="15"/>
-    <row r="151" ht="15.75" customHeight="1" s="15"/>
-    <row r="152" ht="15.75" customHeight="1" s="15"/>
-    <row r="153" ht="15.75" customHeight="1" s="15"/>
-    <row r="154" ht="15.75" customHeight="1" s="15"/>
-    <row r="155" ht="15.75" customHeight="1" s="15"/>
-    <row r="156" ht="15.75" customHeight="1" s="15"/>
-    <row r="157" ht="15.75" customHeight="1" s="15"/>
-    <row r="158" ht="15.75" customHeight="1" s="15"/>
-    <row r="159" ht="15.75" customHeight="1" s="15"/>
-    <row r="160" ht="15.75" customHeight="1" s="15"/>
-    <row r="161" ht="15.75" customHeight="1" s="15"/>
-    <row r="162" ht="15.75" customHeight="1" s="15"/>
-    <row r="163" ht="15.75" customHeight="1" s="15"/>
-    <row r="164" ht="15.75" customHeight="1" s="15"/>
-    <row r="165" ht="15.75" customHeight="1" s="15"/>
-    <row r="166" ht="15.75" customHeight="1" s="15"/>
-    <row r="167" ht="15.75" customHeight="1" s="15"/>
-    <row r="168" ht="15.75" customHeight="1" s="15"/>
-    <row r="169" ht="15.75" customHeight="1" s="15"/>
-    <row r="170" ht="15.75" customHeight="1" s="15"/>
-    <row r="171" ht="15.75" customHeight="1" s="15"/>
-    <row r="172" ht="15.75" customHeight="1" s="15"/>
-    <row r="173" ht="15.75" customHeight="1" s="15"/>
-    <row r="174" ht="15.75" customHeight="1" s="15"/>
-    <row r="175" ht="15.75" customHeight="1" s="15"/>
-    <row r="176" ht="15.75" customHeight="1" s="15"/>
-    <row r="177" ht="15.75" customHeight="1" s="15"/>
-    <row r="178" ht="15.75" customHeight="1" s="15"/>
-    <row r="179" ht="15.75" customHeight="1" s="15"/>
-    <row r="180" ht="15.75" customHeight="1" s="15"/>
-    <row r="181" ht="15.75" customHeight="1" s="15"/>
-    <row r="182" ht="15.75" customHeight="1" s="15"/>
-    <row r="183" ht="15.75" customHeight="1" s="15"/>
-    <row r="184" ht="15.75" customHeight="1" s="15"/>
-    <row r="185" ht="15.75" customHeight="1" s="15"/>
-    <row r="186" ht="15.75" customHeight="1" s="15"/>
-    <row r="187" ht="15.75" customHeight="1" s="15"/>
-    <row r="188" ht="15.75" customHeight="1" s="15"/>
-    <row r="189" ht="15.75" customHeight="1" s="15"/>
-    <row r="190" ht="15.75" customHeight="1" s="15"/>
-    <row r="191" ht="15.75" customHeight="1" s="15"/>
-    <row r="192" ht="15.75" customHeight="1" s="15"/>
-    <row r="193" ht="15.75" customHeight="1" s="15"/>
-    <row r="194" ht="15.75" customHeight="1" s="15"/>
-    <row r="195" ht="15.75" customHeight="1" s="15"/>
-    <row r="196" ht="15.75" customHeight="1" s="15"/>
-    <row r="197" ht="15.75" customHeight="1" s="15"/>
-    <row r="198" ht="15.75" customHeight="1" s="15"/>
-    <row r="199" ht="15.75" customHeight="1" s="15"/>
-    <row r="200" ht="15.75" customHeight="1" s="15"/>
-    <row r="201" ht="15.75" customHeight="1" s="15"/>
-    <row r="202" ht="15.75" customHeight="1" s="15"/>
-    <row r="203" ht="15.75" customHeight="1" s="15"/>
-    <row r="204" ht="15.75" customHeight="1" s="15"/>
-    <row r="205" ht="15.75" customHeight="1" s="15"/>
-    <row r="206" ht="15.75" customHeight="1" s="15"/>
-    <row r="207" ht="15.75" customHeight="1" s="15"/>
-    <row r="208" ht="15.75" customHeight="1" s="15"/>
-    <row r="209" ht="15.75" customHeight="1" s="15"/>
-    <row r="210" ht="15.75" customHeight="1" s="15"/>
-    <row r="211" ht="15.75" customHeight="1" s="15"/>
-    <row r="212" ht="15.75" customHeight="1" s="15"/>
-    <row r="213" ht="15.75" customHeight="1" s="15"/>
-    <row r="214" ht="15.75" customHeight="1" s="15"/>
-    <row r="215" ht="15.75" customHeight="1" s="15"/>
-    <row r="216" ht="15.75" customHeight="1" s="15"/>
-    <row r="217" ht="15.75" customHeight="1" s="15"/>
-    <row r="218" ht="15.75" customHeight="1" s="15"/>
-    <row r="219" ht="15.75" customHeight="1" s="15"/>
-    <row r="220" ht="15.75" customHeight="1" s="15"/>
-    <row r="221" ht="15.75" customHeight="1" s="15"/>
-    <row r="222" ht="15.75" customHeight="1" s="15"/>
-    <row r="223" ht="15.75" customHeight="1" s="15"/>
-    <row r="224" ht="15.75" customHeight="1" s="15"/>
-    <row r="225" ht="15.75" customHeight="1" s="15"/>
-    <row r="226" ht="15.75" customHeight="1" s="15"/>
-    <row r="227" ht="15.75" customHeight="1" s="15"/>
-    <row r="228" ht="15.75" customHeight="1" s="15"/>
-    <row r="229" ht="15.75" customHeight="1" s="15"/>
-    <row r="230" ht="15.75" customHeight="1" s="15"/>
-    <row r="231" ht="15.75" customHeight="1" s="15"/>
-    <row r="232" ht="15.75" customHeight="1" s="15"/>
-    <row r="233" ht="15.75" customHeight="1" s="15"/>
-    <row r="234" ht="15.75" customHeight="1" s="15"/>
-    <row r="235" ht="15.75" customHeight="1" s="15"/>
-    <row r="236" ht="15.75" customHeight="1" s="15"/>
-    <row r="237" ht="15.75" customHeight="1" s="15"/>
-    <row r="238" ht="15.75" customHeight="1" s="15"/>
-    <row r="239" ht="15.75" customHeight="1" s="15"/>
-    <row r="240" ht="15.75" customHeight="1" s="15"/>
-    <row r="241" ht="15.75" customHeight="1" s="15"/>
-    <row r="242" ht="15.75" customHeight="1" s="15"/>
-    <row r="243" ht="15.75" customHeight="1" s="15"/>
-    <row r="244" ht="15.75" customHeight="1" s="15"/>
-    <row r="245" ht="15.75" customHeight="1" s="15"/>
-    <row r="246" ht="15.75" customHeight="1" s="15"/>
-    <row r="247" ht="15.75" customHeight="1" s="15"/>
-    <row r="248" ht="15.75" customHeight="1" s="15"/>
-    <row r="249" ht="15.75" customHeight="1" s="15"/>
-    <row r="250" ht="15.75" customHeight="1" s="15"/>
-    <row r="251" ht="15.75" customHeight="1" s="15"/>
-    <row r="252" ht="15.75" customHeight="1" s="15"/>
-    <row r="253" ht="15.75" customHeight="1" s="15"/>
-    <row r="254" ht="15.75" customHeight="1" s="15"/>
-    <row r="255" ht="15.75" customHeight="1" s="15"/>
-    <row r="256" ht="15.75" customHeight="1" s="15"/>
-    <row r="257" ht="15.75" customHeight="1" s="15"/>
-    <row r="258" ht="15.75" customHeight="1" s="15"/>
-    <row r="259" ht="15.75" customHeight="1" s="15"/>
-    <row r="260" ht="15.75" customHeight="1" s="15"/>
-    <row r="261" ht="15.75" customHeight="1" s="15"/>
-    <row r="262" ht="15.75" customHeight="1" s="15"/>
-    <row r="263" ht="15.75" customHeight="1" s="15"/>
-    <row r="264" ht="15.75" customHeight="1" s="15"/>
-    <row r="265" ht="15.75" customHeight="1" s="15"/>
-    <row r="266" ht="15.75" customHeight="1" s="15"/>
-    <row r="267" ht="15.75" customHeight="1" s="15"/>
-    <row r="268" ht="15.75" customHeight="1" s="15"/>
-    <row r="269" ht="15.75" customHeight="1" s="15"/>
-    <row r="270" ht="15.75" customHeight="1" s="15"/>
-    <row r="271" ht="15.75" customHeight="1" s="15"/>
-    <row r="272" ht="15.75" customHeight="1" s="15"/>
-    <row r="273" ht="15.75" customHeight="1" s="15"/>
-    <row r="274" ht="15.75" customHeight="1" s="15"/>
-    <row r="275" ht="15.75" customHeight="1" s="15"/>
-    <row r="276" ht="15.75" customHeight="1" s="15"/>
-    <row r="277" ht="15.75" customHeight="1" s="15"/>
-    <row r="278" ht="15.75" customHeight="1" s="15"/>
-    <row r="279" ht="15.75" customHeight="1" s="15"/>
-    <row r="280" ht="15.75" customHeight="1" s="15"/>
-    <row r="281" ht="15.75" customHeight="1" s="15"/>
-    <row r="282" ht="15.75" customHeight="1" s="15"/>
-    <row r="283" ht="15.75" customHeight="1" s="15"/>
-    <row r="284" ht="15.75" customHeight="1" s="15"/>
-    <row r="285" ht="15.75" customHeight="1" s="15"/>
-    <row r="286" ht="15.75" customHeight="1" s="15"/>
-    <row r="287" ht="15.75" customHeight="1" s="15"/>
-    <row r="288" ht="15.75" customHeight="1" s="15"/>
-    <row r="289" ht="15.75" customHeight="1" s="15"/>
-    <row r="290" ht="15.75" customHeight="1" s="15"/>
-    <row r="291" ht="15.75" customHeight="1" s="15"/>
-    <row r="292" ht="15.75" customHeight="1" s="15"/>
-    <row r="293" ht="15.75" customHeight="1" s="15"/>
-    <row r="294" ht="15.75" customHeight="1" s="15"/>
-    <row r="295" ht="15.75" customHeight="1" s="15"/>
-    <row r="296" ht="15.75" customHeight="1" s="15"/>
-    <row r="297" ht="15.75" customHeight="1" s="15"/>
-    <row r="298" ht="15.75" customHeight="1" s="15"/>
-    <row r="299" ht="15.75" customHeight="1" s="15"/>
-    <row r="300" ht="15.75" customHeight="1" s="15"/>
-    <row r="301" ht="15.75" customHeight="1" s="15"/>
-    <row r="302" ht="15.75" customHeight="1" s="15"/>
-    <row r="303" ht="15.75" customHeight="1" s="15"/>
-    <row r="304" ht="15.75" customHeight="1" s="15"/>
-    <row r="305" ht="15.75" customHeight="1" s="15"/>
-    <row r="306" ht="15.75" customHeight="1" s="15"/>
-    <row r="307" ht="15.75" customHeight="1" s="15"/>
-    <row r="308" ht="15.75" customHeight="1" s="15"/>
-    <row r="309" ht="15.75" customHeight="1" s="15"/>
-    <row r="310" ht="15.75" customHeight="1" s="15"/>
-    <row r="311" ht="15.75" customHeight="1" s="15"/>
-    <row r="312" ht="15.75" customHeight="1" s="15"/>
-    <row r="313" ht="15.75" customHeight="1" s="15"/>
-    <row r="314" ht="15.75" customHeight="1" s="15"/>
-    <row r="315" ht="15.75" customHeight="1" s="15"/>
-    <row r="316" ht="15.75" customHeight="1" s="15"/>
-    <row r="317" ht="15.75" customHeight="1" s="15"/>
-    <row r="318" ht="15.75" customHeight="1" s="15"/>
-    <row r="319" ht="15.75" customHeight="1" s="15"/>
-    <row r="320" ht="15.75" customHeight="1" s="15"/>
-    <row r="321" ht="15.75" customHeight="1" s="15"/>
-    <row r="322" ht="15.75" customHeight="1" s="15"/>
-    <row r="323" ht="15.75" customHeight="1" s="15"/>
-    <row r="324" ht="15.75" customHeight="1" s="15"/>
-    <row r="325" ht="15.75" customHeight="1" s="15"/>
-    <row r="326" ht="15.75" customHeight="1" s="15"/>
-    <row r="327" ht="15.75" customHeight="1" s="15"/>
-    <row r="328" ht="15.75" customHeight="1" s="15"/>
-    <row r="329" ht="15.75" customHeight="1" s="15"/>
-    <row r="330" ht="15.75" customHeight="1" s="15"/>
-    <row r="331" ht="15.75" customHeight="1" s="15"/>
-    <row r="332" ht="15.75" customHeight="1" s="15"/>
-    <row r="333" ht="15.75" customHeight="1" s="15"/>
-    <row r="334" ht="15.75" customHeight="1" s="15"/>
-    <row r="335" ht="15.75" customHeight="1" s="15"/>
-    <row r="336" ht="15.75" customHeight="1" s="15"/>
-    <row r="337" ht="15.75" customHeight="1" s="15"/>
-    <row r="338" ht="15.75" customHeight="1" s="15"/>
-    <row r="339" ht="15.75" customHeight="1" s="15"/>
-    <row r="340" ht="15.75" customHeight="1" s="15"/>
-    <row r="341" ht="15.75" customHeight="1" s="15"/>
-    <row r="342" ht="15.75" customHeight="1" s="15"/>
-    <row r="343" ht="15.75" customHeight="1" s="15"/>
-    <row r="344" ht="15.75" customHeight="1" s="15"/>
-    <row r="345" ht="15.75" customHeight="1" s="15"/>
-    <row r="346" ht="15.75" customHeight="1" s="15"/>
-    <row r="347" ht="15.75" customHeight="1" s="15"/>
-    <row r="348" ht="15.75" customHeight="1" s="15"/>
-    <row r="349" ht="15.75" customHeight="1" s="15"/>
-    <row r="350" ht="15.75" customHeight="1" s="15"/>
-    <row r="351" ht="15.75" customHeight="1" s="15"/>
-    <row r="352" ht="15.75" customHeight="1" s="15"/>
-    <row r="353" ht="15.75" customHeight="1" s="15"/>
-    <row r="354" ht="15.75" customHeight="1" s="15"/>
-    <row r="355" ht="15.75" customHeight="1" s="15"/>
-    <row r="356" ht="15.75" customHeight="1" s="15"/>
-    <row r="357" ht="15.75" customHeight="1" s="15"/>
-    <row r="358" ht="15.75" customHeight="1" s="15"/>
-    <row r="359" ht="15.75" customHeight="1" s="15"/>
-    <row r="360" ht="15.75" customHeight="1" s="15"/>
-    <row r="361" ht="15.75" customHeight="1" s="15"/>
-    <row r="362" ht="15.75" customHeight="1" s="15"/>
-    <row r="363" ht="15.75" customHeight="1" s="15"/>
-    <row r="364" ht="15.75" customHeight="1" s="15"/>
-    <row r="365" ht="15.75" customHeight="1" s="15"/>
-    <row r="366" ht="15.75" customHeight="1" s="15"/>
-    <row r="367" ht="15.75" customHeight="1" s="15"/>
-    <row r="368" ht="15.75" customHeight="1" s="15"/>
-    <row r="369" ht="15.75" customHeight="1" s="15"/>
-    <row r="370" ht="15.75" customHeight="1" s="15"/>
-    <row r="371" ht="15.75" customHeight="1" s="15"/>
-    <row r="372" ht="15.75" customHeight="1" s="15"/>
-    <row r="373" ht="15.75" customHeight="1" s="15"/>
-    <row r="374" ht="15.75" customHeight="1" s="15"/>
-    <row r="375" ht="15.75" customHeight="1" s="15"/>
-    <row r="376" ht="15.75" customHeight="1" s="15"/>
-    <row r="377" ht="15.75" customHeight="1" s="15"/>
-    <row r="378" ht="15.75" customHeight="1" s="15"/>
-    <row r="379" ht="15.75" customHeight="1" s="15"/>
-    <row r="380" ht="15.75" customHeight="1" s="15"/>
-    <row r="381" ht="15.75" customHeight="1" s="15"/>
-    <row r="382" ht="15.75" customHeight="1" s="15"/>
-    <row r="383" ht="15.75" customHeight="1" s="15"/>
-    <row r="384" ht="15.75" customHeight="1" s="15"/>
-    <row r="385" ht="15.75" customHeight="1" s="15"/>
-    <row r="386" ht="15.75" customHeight="1" s="15"/>
-    <row r="387" ht="15.75" customHeight="1" s="15"/>
-    <row r="388" ht="15.75" customHeight="1" s="15"/>
-    <row r="389" ht="15.75" customHeight="1" s="15"/>
-    <row r="390" ht="15.75" customHeight="1" s="15"/>
-    <row r="391" ht="15.75" customHeight="1" s="15"/>
-    <row r="392" ht="15.75" customHeight="1" s="15"/>
-    <row r="393" ht="15.75" customHeight="1" s="15"/>
-    <row r="394" ht="15.75" customHeight="1" s="15"/>
-    <row r="395" ht="15.75" customHeight="1" s="15"/>
-    <row r="396" ht="15.75" customHeight="1" s="15"/>
-    <row r="397" ht="15.75" customHeight="1" s="15"/>
-    <row r="398" ht="15.75" customHeight="1" s="15"/>
-    <row r="399" ht="15.75" customHeight="1" s="15"/>
-    <row r="400" ht="15.75" customHeight="1" s="15"/>
-    <row r="401" ht="15.75" customHeight="1" s="15"/>
-    <row r="402" ht="15.75" customHeight="1" s="15"/>
-    <row r="403" ht="15.75" customHeight="1" s="15"/>
-    <row r="404" ht="15.75" customHeight="1" s="15"/>
-    <row r="405" ht="15.75" customHeight="1" s="15"/>
-    <row r="406" ht="15.75" customHeight="1" s="15"/>
-    <row r="407" ht="15.75" customHeight="1" s="15"/>
-    <row r="408" ht="15.75" customHeight="1" s="15"/>
-    <row r="409" ht="15.75" customHeight="1" s="15"/>
-    <row r="410" ht="15.75" customHeight="1" s="15"/>
-    <row r="411" ht="15.75" customHeight="1" s="15"/>
-    <row r="412" ht="15.75" customHeight="1" s="15"/>
-    <row r="413" ht="15.75" customHeight="1" s="15"/>
-    <row r="414" ht="15.75" customHeight="1" s="15"/>
-    <row r="415" ht="15.75" customHeight="1" s="15"/>
-    <row r="416" ht="15.75" customHeight="1" s="15"/>
-    <row r="417" ht="15.75" customHeight="1" s="15"/>
-    <row r="418" ht="15.75" customHeight="1" s="15"/>
-    <row r="419" ht="15.75" customHeight="1" s="15"/>
-    <row r="420" ht="15.75" customHeight="1" s="15"/>
-    <row r="421" ht="15.75" customHeight="1" s="15"/>
-    <row r="422" ht="15.75" customHeight="1" s="15"/>
-    <row r="423" ht="15.75" customHeight="1" s="15"/>
-    <row r="424" ht="15.75" customHeight="1" s="15"/>
-    <row r="425" ht="15.75" customHeight="1" s="15"/>
-    <row r="426" ht="15.75" customHeight="1" s="15"/>
-    <row r="427" ht="15.75" customHeight="1" s="15"/>
-    <row r="428" ht="15.75" customHeight="1" s="15"/>
-    <row r="429" ht="15.75" customHeight="1" s="15"/>
-    <row r="430" ht="15.75" customHeight="1" s="15"/>
-    <row r="431" ht="15.75" customHeight="1" s="15"/>
-    <row r="432" ht="15.75" customHeight="1" s="15"/>
-    <row r="433" ht="15.75" customHeight="1" s="15"/>
-    <row r="434" ht="15.75" customHeight="1" s="15"/>
-    <row r="435" ht="15.75" customHeight="1" s="15"/>
-    <row r="436" ht="15.75" customHeight="1" s="15"/>
-    <row r="437" ht="15.75" customHeight="1" s="15"/>
-    <row r="438" ht="15.75" customHeight="1" s="15"/>
-    <row r="439" ht="15.75" customHeight="1" s="15"/>
-    <row r="440" ht="15.75" customHeight="1" s="15"/>
-    <row r="441" ht="15.75" customHeight="1" s="15"/>
-    <row r="442" ht="15.75" customHeight="1" s="15"/>
-    <row r="443" ht="15.75" customHeight="1" s="15"/>
-    <row r="444" ht="15.75" customHeight="1" s="15"/>
-    <row r="445" ht="15.75" customHeight="1" s="15"/>
-    <row r="446" ht="15.75" customHeight="1" s="15"/>
-    <row r="447" ht="15.75" customHeight="1" s="15"/>
-    <row r="448" ht="15.75" customHeight="1" s="15"/>
-    <row r="449" ht="15.75" customHeight="1" s="15"/>
-    <row r="450" ht="15.75" customHeight="1" s="15"/>
-    <row r="451" ht="15.75" customHeight="1" s="15"/>
-    <row r="452" ht="15.75" customHeight="1" s="15"/>
-    <row r="453" ht="15.75" customHeight="1" s="15"/>
-    <row r="454" ht="15.75" customHeight="1" s="15"/>
-    <row r="455" ht="15.75" customHeight="1" s="15"/>
-    <row r="456" ht="15.75" customHeight="1" s="15"/>
-    <row r="457" ht="15.75" customHeight="1" s="15"/>
-    <row r="458" ht="15.75" customHeight="1" s="15"/>
-    <row r="459" ht="15.75" customHeight="1" s="15"/>
-    <row r="460" ht="15.75" customHeight="1" s="15"/>
-    <row r="461" ht="15.75" customHeight="1" s="15"/>
-    <row r="462" ht="15.75" customHeight="1" s="15"/>
-    <row r="463" ht="15.75" customHeight="1" s="15"/>
-    <row r="464" ht="15.75" customHeight="1" s="15"/>
-    <row r="465" ht="15.75" customHeight="1" s="15"/>
-    <row r="466" ht="15.75" customHeight="1" s="15"/>
-    <row r="467" ht="15.75" customHeight="1" s="15"/>
-    <row r="468" ht="15.75" customHeight="1" s="15"/>
-    <row r="469" ht="15.75" customHeight="1" s="15"/>
-    <row r="470" ht="15.75" customHeight="1" s="15"/>
-    <row r="471" ht="15.75" customHeight="1" s="15"/>
-    <row r="472" ht="15.75" customHeight="1" s="15"/>
-    <row r="473" ht="15.75" customHeight="1" s="15"/>
-    <row r="474" ht="15.75" customHeight="1" s="15"/>
-    <row r="475" ht="15.75" customHeight="1" s="15"/>
-    <row r="476" ht="15.75" customHeight="1" s="15"/>
-    <row r="477" ht="15.75" customHeight="1" s="15"/>
-    <row r="478" ht="15.75" customHeight="1" s="15"/>
-    <row r="479" ht="15.75" customHeight="1" s="15"/>
-    <row r="480" ht="15.75" customHeight="1" s="15"/>
-    <row r="481" ht="15.75" customHeight="1" s="15"/>
-    <row r="482" ht="15.75" customHeight="1" s="15"/>
-    <row r="483" ht="15.75" customHeight="1" s="15"/>
-    <row r="484" ht="15.75" customHeight="1" s="15"/>
-    <row r="485" ht="15.75" customHeight="1" s="15"/>
-    <row r="486" ht="15.75" customHeight="1" s="15"/>
-    <row r="487" ht="15.75" customHeight="1" s="15"/>
-    <row r="488" ht="15.75" customHeight="1" s="15"/>
-    <row r="489" ht="15.75" customHeight="1" s="15"/>
-    <row r="490" ht="15.75" customHeight="1" s="15"/>
-    <row r="491" ht="15.75" customHeight="1" s="15"/>
-    <row r="492" ht="15.75" customHeight="1" s="15"/>
-    <row r="493" ht="15.75" customHeight="1" s="15"/>
-    <row r="494" ht="15.75" customHeight="1" s="15"/>
-    <row r="495" ht="15.75" customHeight="1" s="15"/>
-    <row r="496" ht="15.75" customHeight="1" s="15"/>
-    <row r="497" ht="15.75" customHeight="1" s="15"/>
-    <row r="498" ht="15.75" customHeight="1" s="15"/>
-    <row r="499" ht="15.75" customHeight="1" s="15"/>
-    <row r="500" ht="15.75" customHeight="1" s="15"/>
-    <row r="501" ht="15.75" customHeight="1" s="15"/>
-    <row r="502" ht="15.75" customHeight="1" s="15"/>
-    <row r="503" ht="15.75" customHeight="1" s="15"/>
-    <row r="504" ht="15.75" customHeight="1" s="15"/>
-    <row r="505" ht="15.75" customHeight="1" s="15"/>
-    <row r="506" ht="15.75" customHeight="1" s="15"/>
-    <row r="507" ht="15.75" customHeight="1" s="15"/>
-    <row r="508" ht="15.75" customHeight="1" s="15"/>
-    <row r="509" ht="15.75" customHeight="1" s="15"/>
-    <row r="510" ht="15.75" customHeight="1" s="15"/>
-    <row r="511" ht="15.75" customHeight="1" s="15"/>
-    <row r="512" ht="15.75" customHeight="1" s="15"/>
-    <row r="513" ht="15.75" customHeight="1" s="15"/>
-    <row r="514" ht="15.75" customHeight="1" s="15"/>
-    <row r="515" ht="15.75" customHeight="1" s="15"/>
-    <row r="516" ht="15.75" customHeight="1" s="15"/>
-    <row r="517" ht="15.75" customHeight="1" s="15"/>
-    <row r="518" ht="15.75" customHeight="1" s="15"/>
-    <row r="519" ht="15.75" customHeight="1" s="15"/>
-    <row r="520" ht="15.75" customHeight="1" s="15"/>
-    <row r="521" ht="15.75" customHeight="1" s="15"/>
-    <row r="522" ht="15.75" customHeight="1" s="15"/>
-    <row r="523" ht="15.75" customHeight="1" s="15"/>
-    <row r="524" ht="15.75" customHeight="1" s="15"/>
-    <row r="525" ht="15.75" customHeight="1" s="15"/>
-    <row r="526" ht="15.75" customHeight="1" s="15"/>
-    <row r="527" ht="15.75" customHeight="1" s="15"/>
-    <row r="528" ht="15.75" customHeight="1" s="15"/>
-    <row r="529" ht="15.75" customHeight="1" s="15"/>
-    <row r="530" ht="15.75" customHeight="1" s="15"/>
-    <row r="531" ht="15.75" customHeight="1" s="15"/>
-    <row r="532" ht="15.75" customHeight="1" s="15"/>
-    <row r="533" ht="15.75" customHeight="1" s="15"/>
-    <row r="534" ht="15.75" customHeight="1" s="15"/>
-    <row r="535" ht="15.75" customHeight="1" s="15"/>
-    <row r="536" ht="15.75" customHeight="1" s="15"/>
-    <row r="537" ht="15.75" customHeight="1" s="15"/>
-    <row r="538" ht="15.75" customHeight="1" s="15"/>
-    <row r="539" ht="15.75" customHeight="1" s="15"/>
-    <row r="540" ht="15.75" customHeight="1" s="15"/>
-    <row r="541" ht="15.75" customHeight="1" s="15"/>
-    <row r="542" ht="15.75" customHeight="1" s="15"/>
-    <row r="543" ht="15.75" customHeight="1" s="15"/>
-    <row r="544" ht="15.75" customHeight="1" s="15"/>
-    <row r="545" ht="15.75" customHeight="1" s="15"/>
-    <row r="546" ht="15.75" customHeight="1" s="15"/>
-    <row r="547" ht="15.75" customHeight="1" s="15"/>
-    <row r="548" ht="15.75" customHeight="1" s="15"/>
-    <row r="549" ht="15.75" customHeight="1" s="15"/>
-    <row r="550" ht="15.75" customHeight="1" s="15"/>
-    <row r="551" ht="15.75" customHeight="1" s="15"/>
-    <row r="552" ht="15.75" customHeight="1" s="15"/>
-    <row r="553" ht="15.75" customHeight="1" s="15"/>
-    <row r="554" ht="15.75" customHeight="1" s="15"/>
-    <row r="555" ht="15.75" customHeight="1" s="15"/>
-    <row r="556" ht="15.75" customHeight="1" s="15"/>
-    <row r="557" ht="15.75" customHeight="1" s="15"/>
-    <row r="558" ht="15.75" customHeight="1" s="15"/>
-    <row r="559" ht="15.75" customHeight="1" s="15"/>
-    <row r="560" ht="15.75" customHeight="1" s="15"/>
-    <row r="561" ht="15.75" customHeight="1" s="15"/>
-    <row r="562" ht="15.75" customHeight="1" s="15"/>
-    <row r="563" ht="15.75" customHeight="1" s="15"/>
-    <row r="564" ht="15.75" customHeight="1" s="15"/>
-    <row r="565" ht="15.75" customHeight="1" s="15"/>
-    <row r="566" ht="15.75" customHeight="1" s="15"/>
-    <row r="567" ht="15.75" customHeight="1" s="15"/>
-    <row r="568" ht="15.75" customHeight="1" s="15"/>
-    <row r="569" ht="15.75" customHeight="1" s="15"/>
-    <row r="570" ht="15.75" customHeight="1" s="15"/>
-    <row r="571" ht="15.75" customHeight="1" s="15"/>
-    <row r="572" ht="15.75" customHeight="1" s="15"/>
-    <row r="573" ht="15.75" customHeight="1" s="15"/>
-    <row r="574" ht="15.75" customHeight="1" s="15"/>
-    <row r="575" ht="15.75" customHeight="1" s="15"/>
-    <row r="576" ht="15.75" customHeight="1" s="15"/>
-    <row r="577" ht="15.75" customHeight="1" s="15"/>
-    <row r="578" ht="15.75" customHeight="1" s="15"/>
-    <row r="579" ht="15.75" customHeight="1" s="15"/>
-    <row r="580" ht="15.75" customHeight="1" s="15"/>
-    <row r="581" ht="15.75" customHeight="1" s="15"/>
-    <row r="582" ht="15.75" customHeight="1" s="15"/>
-    <row r="583" ht="15.75" customHeight="1" s="15"/>
-    <row r="584" ht="15.75" customHeight="1" s="15"/>
-    <row r="585" ht="15.75" customHeight="1" s="15"/>
-    <row r="586" ht="15.75" customHeight="1" s="15"/>
-    <row r="587" ht="15.75" customHeight="1" s="15"/>
-    <row r="588" ht="15.75" customHeight="1" s="15"/>
-    <row r="589" ht="15.75" customHeight="1" s="15"/>
-    <row r="590" ht="15.75" customHeight="1" s="15"/>
-    <row r="591" ht="15.75" customHeight="1" s="15"/>
-    <row r="592" ht="15.75" customHeight="1" s="15"/>
-    <row r="593" ht="15.75" customHeight="1" s="15"/>
-    <row r="594" ht="15.75" customHeight="1" s="15"/>
-    <row r="595" ht="15.75" customHeight="1" s="15"/>
-    <row r="596" ht="15.75" customHeight="1" s="15"/>
-    <row r="597" ht="15.75" customHeight="1" s="15"/>
-    <row r="598" ht="15.75" customHeight="1" s="15"/>
-    <row r="599" ht="15.75" customHeight="1" s="15"/>
-    <row r="600" ht="15.75" customHeight="1" s="15"/>
-    <row r="601" ht="15.75" customHeight="1" s="15"/>
-    <row r="602" ht="15.75" customHeight="1" s="15"/>
-    <row r="603" ht="15.75" customHeight="1" s="15"/>
-    <row r="604" ht="15.75" customHeight="1" s="15"/>
-    <row r="605" ht="15.75" customHeight="1" s="15"/>
-    <row r="606" ht="15.75" customHeight="1" s="15"/>
-    <row r="607" ht="15.75" customHeight="1" s="15"/>
-    <row r="608" ht="15.75" customHeight="1" s="15"/>
-    <row r="609" ht="15.75" customHeight="1" s="15"/>
-    <row r="610" ht="15.75" customHeight="1" s="15"/>
-    <row r="611" ht="15.75" customHeight="1" s="15"/>
-    <row r="612" ht="15.75" customHeight="1" s="15"/>
-    <row r="613" ht="15.75" customHeight="1" s="15"/>
-    <row r="614" ht="15.75" customHeight="1" s="15"/>
-    <row r="615" ht="15.75" customHeight="1" s="15"/>
-    <row r="616" ht="15.75" customHeight="1" s="15"/>
-    <row r="617" ht="15.75" customHeight="1" s="15"/>
-    <row r="618" ht="15.75" customHeight="1" s="15"/>
-    <row r="619" ht="15.75" customHeight="1" s="15"/>
-    <row r="620" ht="15.75" customHeight="1" s="15"/>
-    <row r="621" ht="15.75" customHeight="1" s="15"/>
-    <row r="622" ht="15.75" customHeight="1" s="15"/>
-    <row r="623" ht="15.75" customHeight="1" s="15"/>
-    <row r="624" ht="15.75" customHeight="1" s="15"/>
-    <row r="625" ht="15.75" customHeight="1" s="15"/>
-    <row r="626" ht="15.75" customHeight="1" s="15"/>
-    <row r="627" ht="15.75" customHeight="1" s="15"/>
-    <row r="628" ht="15.75" customHeight="1" s="15"/>
-    <row r="629" ht="15.75" customHeight="1" s="15"/>
-    <row r="630" ht="15.75" customHeight="1" s="15"/>
-    <row r="631" ht="15.75" customHeight="1" s="15"/>
-    <row r="632" ht="15.75" customHeight="1" s="15"/>
-    <row r="633" ht="15.75" customHeight="1" s="15"/>
-    <row r="634" ht="15.75" customHeight="1" s="15"/>
-    <row r="635" ht="15.75" customHeight="1" s="15"/>
-    <row r="636" ht="15.75" customHeight="1" s="15"/>
-    <row r="637" ht="15.75" customHeight="1" s="15"/>
-    <row r="638" ht="15.75" customHeight="1" s="15"/>
-    <row r="639" ht="15.75" customHeight="1" s="15"/>
-    <row r="640" ht="15.75" customHeight="1" s="15"/>
-    <row r="641" ht="15.75" customHeight="1" s="15"/>
-    <row r="642" ht="15.75" customHeight="1" s="15"/>
-    <row r="643" ht="15.75" customHeight="1" s="15"/>
-    <row r="644" ht="15.75" customHeight="1" s="15"/>
-    <row r="645" ht="15.75" customHeight="1" s="15"/>
-    <row r="646" ht="15.75" customHeight="1" s="15"/>
-    <row r="647" ht="15.75" customHeight="1" s="15"/>
-    <row r="648" ht="15.75" customHeight="1" s="15"/>
-    <row r="649" ht="15.75" customHeight="1" s="15"/>
-    <row r="650" ht="15.75" customHeight="1" s="15"/>
-    <row r="651" ht="15.75" customHeight="1" s="15"/>
-    <row r="652" ht="15.75" customHeight="1" s="15"/>
-    <row r="653" ht="15.75" customHeight="1" s="15"/>
-    <row r="654" ht="15.75" customHeight="1" s="15"/>
-    <row r="655" ht="15.75" customHeight="1" s="15"/>
-    <row r="656" ht="15.75" customHeight="1" s="15"/>
-    <row r="657" ht="15.75" customHeight="1" s="15"/>
-    <row r="658" ht="15.75" customHeight="1" s="15"/>
-    <row r="659" ht="15.75" customHeight="1" s="15"/>
-    <row r="660" ht="15.75" customHeight="1" s="15"/>
-    <row r="661" ht="15.75" customHeight="1" s="15"/>
-    <row r="662" ht="15.75" customHeight="1" s="15"/>
-    <row r="663" ht="15.75" customHeight="1" s="15"/>
-    <row r="664" ht="15.75" customHeight="1" s="15"/>
-    <row r="665" ht="15.75" customHeight="1" s="15"/>
-    <row r="666" ht="15.75" customHeight="1" s="15"/>
-    <row r="667" ht="15.75" customHeight="1" s="15"/>
-    <row r="668" ht="15.75" customHeight="1" s="15"/>
-    <row r="669" ht="15.75" customHeight="1" s="15"/>
-    <row r="670" ht="15.75" customHeight="1" s="15"/>
-    <row r="671" ht="15.75" customHeight="1" s="15"/>
-    <row r="672" ht="15.75" customHeight="1" s="15"/>
-    <row r="673" ht="15.75" customHeight="1" s="15"/>
-    <row r="674" ht="15.75" customHeight="1" s="15"/>
-    <row r="675" ht="15.75" customHeight="1" s="15"/>
-    <row r="676" ht="15.75" customHeight="1" s="15"/>
-    <row r="677" ht="15.75" customHeight="1" s="15"/>
-    <row r="678" ht="15.75" customHeight="1" s="15"/>
-    <row r="679" ht="15.75" customHeight="1" s="15"/>
-    <row r="680" ht="15.75" customHeight="1" s="15"/>
-    <row r="681" ht="15.75" customHeight="1" s="15"/>
-    <row r="682" ht="15.75" customHeight="1" s="15"/>
-    <row r="683" ht="15.75" customHeight="1" s="15"/>
-    <row r="684" ht="15.75" customHeight="1" s="15"/>
-    <row r="685" ht="15.75" customHeight="1" s="15"/>
-    <row r="686" ht="15.75" customHeight="1" s="15"/>
-    <row r="687" ht="15.75" customHeight="1" s="15"/>
-    <row r="688" ht="15.75" customHeight="1" s="15"/>
-    <row r="689" ht="15.75" customHeight="1" s="15"/>
-    <row r="690" ht="15.75" customHeight="1" s="15"/>
-    <row r="691" ht="15.75" customHeight="1" s="15"/>
-    <row r="692" ht="15.75" customHeight="1" s="15"/>
-    <row r="693" ht="15.75" customHeight="1" s="15"/>
-    <row r="694" ht="15.75" customHeight="1" s="15"/>
-    <row r="695" ht="15.75" customHeight="1" s="15"/>
-    <row r="696" ht="15.75" customHeight="1" s="15"/>
-    <row r="697" ht="15.75" customHeight="1" s="15"/>
-    <row r="698" ht="15.75" customHeight="1" s="15"/>
-    <row r="699" ht="15.75" customHeight="1" s="15"/>
-    <row r="700" ht="15.75" customHeight="1" s="15"/>
-    <row r="701" ht="15.75" customHeight="1" s="15"/>
-    <row r="702" ht="15.75" customHeight="1" s="15"/>
-    <row r="703" ht="15.75" customHeight="1" s="15"/>
-    <row r="704" ht="15.75" customHeight="1" s="15"/>
-    <row r="705" ht="15.75" customHeight="1" s="15"/>
-    <row r="706" ht="15.75" customHeight="1" s="15"/>
-    <row r="707" ht="15.75" customHeight="1" s="15"/>
-    <row r="708" ht="15.75" customHeight="1" s="15"/>
-    <row r="709" ht="15.75" customHeight="1" s="15"/>
-    <row r="710" ht="15.75" customHeight="1" s="15"/>
-    <row r="711" ht="15.75" customHeight="1" s="15"/>
-    <row r="712" ht="15.75" customHeight="1" s="15"/>
-    <row r="713" ht="15.75" customHeight="1" s="15"/>
-    <row r="714" ht="15.75" customHeight="1" s="15"/>
-    <row r="715" ht="15.75" customHeight="1" s="15"/>
-    <row r="716" ht="15.75" customHeight="1" s="15"/>
-    <row r="717" ht="15.75" customHeight="1" s="15"/>
-    <row r="718" ht="15.75" customHeight="1" s="15"/>
-    <row r="719" ht="15.75" customHeight="1" s="15"/>
-    <row r="720" ht="15.75" customHeight="1" s="15"/>
-    <row r="721" ht="15.75" customHeight="1" s="15"/>
-    <row r="722" ht="15.75" customHeight="1" s="15"/>
-    <row r="723" ht="15.75" customHeight="1" s="15"/>
-    <row r="724" ht="15.75" customHeight="1" s="15"/>
-    <row r="725" ht="15.75" customHeight="1" s="15"/>
-    <row r="726" ht="15.75" customHeight="1" s="15"/>
-    <row r="727" ht="15.75" customHeight="1" s="15"/>
-    <row r="728" ht="15.75" customHeight="1" s="15"/>
-    <row r="729" ht="15.75" customHeight="1" s="15"/>
-    <row r="730" ht="15.75" customHeight="1" s="15"/>
-    <row r="731" ht="15.75" customHeight="1" s="15"/>
-    <row r="732" ht="15.75" customHeight="1" s="15"/>
-    <row r="733" ht="15.75" customHeight="1" s="15"/>
-    <row r="734" ht="15.75" customHeight="1" s="15"/>
-    <row r="735" ht="15.75" customHeight="1" s="15"/>
-    <row r="736" ht="15.75" customHeight="1" s="15"/>
-    <row r="737" ht="15.75" customHeight="1" s="15"/>
-    <row r="738" ht="15.75" customHeight="1" s="15"/>
-    <row r="739" ht="15.75" customHeight="1" s="15"/>
-    <row r="740" ht="15.75" customHeight="1" s="15"/>
-    <row r="741" ht="15.75" customHeight="1" s="15"/>
-    <row r="742" ht="15.75" customHeight="1" s="15"/>
-    <row r="743" ht="15.75" customHeight="1" s="15"/>
-    <row r="744" ht="15.75" customHeight="1" s="15"/>
-    <row r="745" ht="15.75" customHeight="1" s="15"/>
-    <row r="746" ht="15.75" customHeight="1" s="15"/>
-    <row r="747" ht="15.75" customHeight="1" s="15"/>
-    <row r="748" ht="15.75" customHeight="1" s="15"/>
-    <row r="749" ht="15.75" customHeight="1" s="15"/>
-    <row r="750" ht="15.75" customHeight="1" s="15"/>
-    <row r="751" ht="15.75" customHeight="1" s="15"/>
-    <row r="752" ht="15.75" customHeight="1" s="15"/>
-    <row r="753" ht="15.75" customHeight="1" s="15"/>
-    <row r="754" ht="15.75" customHeight="1" s="15"/>
-    <row r="755" ht="15.75" customHeight="1" s="15"/>
-    <row r="756" ht="15.75" customHeight="1" s="15"/>
-    <row r="757" ht="15.75" customHeight="1" s="15"/>
-    <row r="758" ht="15.75" customHeight="1" s="15"/>
-    <row r="759" ht="15.75" customHeight="1" s="15"/>
-    <row r="760" ht="15.75" customHeight="1" s="15"/>
-    <row r="761" ht="15.75" customHeight="1" s="15"/>
-    <row r="762" ht="15.75" customHeight="1" s="15"/>
-    <row r="763" ht="15.75" customHeight="1" s="15"/>
-    <row r="764" ht="15.75" customHeight="1" s="15"/>
-    <row r="765" ht="15.75" customHeight="1" s="15"/>
-    <row r="766" ht="15.75" customHeight="1" s="15"/>
-    <row r="767" ht="15.75" customHeight="1" s="15"/>
-    <row r="768" ht="15.75" customHeight="1" s="15"/>
-    <row r="769" ht="15.75" customHeight="1" s="15"/>
-    <row r="770" ht="15.75" customHeight="1" s="15"/>
-    <row r="771" ht="15.75" customHeight="1" s="15"/>
-    <row r="772" ht="15.75" customHeight="1" s="15"/>
-    <row r="773" ht="15.75" customHeight="1" s="15"/>
-    <row r="774" ht="15.75" customHeight="1" s="15"/>
-    <row r="775" ht="15.75" customHeight="1" s="15"/>
-    <row r="776" ht="15.75" customHeight="1" s="15"/>
-    <row r="777" ht="15.75" customHeight="1" s="15"/>
-    <row r="778" ht="15.75" customHeight="1" s="15"/>
-    <row r="779" ht="15.75" customHeight="1" s="15"/>
-    <row r="780" ht="15.75" customHeight="1" s="15"/>
-    <row r="781" ht="15.75" customHeight="1" s="15"/>
-    <row r="782" ht="15.75" customHeight="1" s="15"/>
-    <row r="783" ht="15.75" customHeight="1" s="15"/>
-    <row r="784" ht="15.75" customHeight="1" s="15"/>
-    <row r="785" ht="15.75" customHeight="1" s="15"/>
-    <row r="786" ht="15.75" customHeight="1" s="15"/>
-    <row r="787" ht="15.75" customHeight="1" s="15"/>
-    <row r="788" ht="15.75" customHeight="1" s="15"/>
-    <row r="789" ht="15.75" customHeight="1" s="15"/>
-    <row r="790" ht="15.75" customHeight="1" s="15"/>
-    <row r="791" ht="15.75" customHeight="1" s="15"/>
-    <row r="792" ht="15.75" customHeight="1" s="15"/>
-    <row r="793" ht="15.75" customHeight="1" s="15"/>
-    <row r="794" ht="15.75" customHeight="1" s="15"/>
-    <row r="795" ht="15.75" customHeight="1" s="15"/>
-    <row r="796" ht="15.75" customHeight="1" s="15"/>
-    <row r="797" ht="15.75" customHeight="1" s="15"/>
-    <row r="798" ht="15.75" customHeight="1" s="15"/>
-    <row r="799" ht="15.75" customHeight="1" s="15"/>
-    <row r="800" ht="15.75" customHeight="1" s="15"/>
-    <row r="801" ht="15.75" customHeight="1" s="15"/>
-    <row r="802" ht="15.75" customHeight="1" s="15"/>
-    <row r="803" ht="15.75" customHeight="1" s="15"/>
-    <row r="804" ht="15.75" customHeight="1" s="15"/>
-    <row r="805" ht="15.75" customHeight="1" s="15"/>
-    <row r="806" ht="15.75" customHeight="1" s="15"/>
-    <row r="807" ht="15.75" customHeight="1" s="15"/>
-    <row r="808" ht="15.75" customHeight="1" s="15"/>
-    <row r="809" ht="15.75" customHeight="1" s="15"/>
-    <row r="810" ht="15.75" customHeight="1" s="15"/>
-    <row r="811" ht="15.75" customHeight="1" s="15"/>
-    <row r="812" ht="15.75" customHeight="1" s="15"/>
-    <row r="813" ht="15.75" customHeight="1" s="15"/>
-    <row r="814" ht="15.75" customHeight="1" s="15"/>
-    <row r="815" ht="15.75" customHeight="1" s="15"/>
-    <row r="816" ht="15.75" customHeight="1" s="15"/>
-    <row r="817" ht="15.75" customHeight="1" s="15"/>
-    <row r="818" ht="15.75" customHeight="1" s="15"/>
-    <row r="819" ht="15.75" customHeight="1" s="15"/>
-    <row r="820" ht="15.75" customHeight="1" s="15"/>
-    <row r="821" ht="15.75" customHeight="1" s="15"/>
-    <row r="822" ht="15.75" customHeight="1" s="15"/>
-    <row r="823" ht="15.75" customHeight="1" s="15"/>
-    <row r="824" ht="15.75" customHeight="1" s="15"/>
-    <row r="825" ht="15.75" customHeight="1" s="15"/>
-    <row r="826" ht="15.75" customHeight="1" s="15"/>
-    <row r="827" ht="15.75" customHeight="1" s="15"/>
-    <row r="828" ht="15.75" customHeight="1" s="15"/>
-    <row r="829" ht="15.75" customHeight="1" s="15"/>
-    <row r="830" ht="15.75" customHeight="1" s="15"/>
-    <row r="831" ht="15.75" customHeight="1" s="15"/>
-    <row r="832" ht="15.75" customHeight="1" s="15"/>
-    <row r="833" ht="15.75" customHeight="1" s="15"/>
-    <row r="834" ht="15.75" customHeight="1" s="15"/>
-    <row r="835" ht="15.75" customHeight="1" s="15"/>
-    <row r="836" ht="15.75" customHeight="1" s="15"/>
-    <row r="837" ht="15.75" customHeight="1" s="15"/>
-    <row r="838" ht="15.75" customHeight="1" s="15"/>
-    <row r="839" ht="15.75" customHeight="1" s="15"/>
-    <row r="840" ht="15.75" customHeight="1" s="15"/>
-    <row r="841" ht="15.75" customHeight="1" s="15"/>
-    <row r="842" ht="15.75" customHeight="1" s="15"/>
-    <row r="843" ht="15.75" customHeight="1" s="15"/>
-    <row r="844" ht="15.75" customHeight="1" s="15"/>
-    <row r="845" ht="15.75" customHeight="1" s="15"/>
-    <row r="846" ht="15.75" customHeight="1" s="15"/>
-    <row r="847" ht="15.75" customHeight="1" s="15"/>
-    <row r="848" ht="15.75" customHeight="1" s="15"/>
-    <row r="849" ht="15.75" customHeight="1" s="15"/>
-    <row r="850" ht="15.75" customHeight="1" s="15"/>
-    <row r="851" ht="15.75" customHeight="1" s="15"/>
-    <row r="852" ht="15.75" customHeight="1" s="15"/>
-    <row r="853" ht="15.75" customHeight="1" s="15"/>
-    <row r="854" ht="15.75" customHeight="1" s="15"/>
-    <row r="855" ht="15.75" customHeight="1" s="15"/>
-    <row r="856" ht="15.75" customHeight="1" s="15"/>
-    <row r="857" ht="15.75" customHeight="1" s="15"/>
-    <row r="858" ht="15.75" customHeight="1" s="15"/>
-    <row r="859" ht="15.75" customHeight="1" s="15"/>
-    <row r="860" ht="15.75" customHeight="1" s="15"/>
-    <row r="861" ht="15.75" customHeight="1" s="15"/>
-    <row r="862" ht="15.75" customHeight="1" s="15"/>
-    <row r="863" ht="15.75" customHeight="1" s="15"/>
-    <row r="864" ht="15.75" customHeight="1" s="15"/>
-    <row r="865" ht="15.75" customHeight="1" s="15"/>
-    <row r="866" ht="15.75" customHeight="1" s="15"/>
-    <row r="867" ht="15.75" customHeight="1" s="15"/>
-    <row r="868" ht="15.75" customHeight="1" s="15"/>
-    <row r="869" ht="15.75" customHeight="1" s="15"/>
-    <row r="870" ht="15.75" customHeight="1" s="15"/>
-    <row r="871" ht="15.75" customHeight="1" s="15"/>
-    <row r="872" ht="15.75" customHeight="1" s="15"/>
-    <row r="873" ht="15.75" customHeight="1" s="15"/>
-    <row r="874" ht="15.75" customHeight="1" s="15"/>
-    <row r="875" ht="15.75" customHeight="1" s="15"/>
-    <row r="876" ht="15.75" customHeight="1" s="15"/>
-    <row r="877" ht="15.75" customHeight="1" s="15"/>
-    <row r="878" ht="15.75" customHeight="1" s="15"/>
-    <row r="879" ht="15.75" customHeight="1" s="15"/>
-    <row r="880" ht="15.75" customHeight="1" s="15"/>
-    <row r="881" ht="15.75" customHeight="1" s="15"/>
-    <row r="882" ht="15.75" customHeight="1" s="15"/>
-    <row r="883" ht="15.75" customHeight="1" s="15"/>
-    <row r="884" ht="15.75" customHeight="1" s="15"/>
-    <row r="885" ht="15.75" customHeight="1" s="15"/>
-    <row r="886" ht="15.75" customHeight="1" s="15"/>
-    <row r="887" ht="15.75" customHeight="1" s="15"/>
-    <row r="888" ht="15.75" customHeight="1" s="15"/>
-    <row r="889" ht="15.75" customHeight="1" s="15"/>
-    <row r="890" ht="15.75" customHeight="1" s="15"/>
-    <row r="891" ht="15.75" customHeight="1" s="15"/>
-    <row r="892" ht="15.75" customHeight="1" s="15"/>
-    <row r="893" ht="15.75" customHeight="1" s="15"/>
-    <row r="894" ht="15.75" customHeight="1" s="15"/>
-    <row r="895" ht="15.75" customHeight="1" s="15"/>
-    <row r="896" ht="15.75" customHeight="1" s="15"/>
-    <row r="897" ht="15.75" customHeight="1" s="15"/>
-    <row r="898" ht="15.75" customHeight="1" s="15"/>
-    <row r="899" ht="15.75" customHeight="1" s="15"/>
-    <row r="900" ht="15.75" customHeight="1" s="15"/>
-    <row r="901" ht="15.75" customHeight="1" s="15"/>
-    <row r="902" ht="15.75" customHeight="1" s="15"/>
-    <row r="903" ht="15.75" customHeight="1" s="15"/>
-    <row r="904" ht="15.75" customHeight="1" s="15"/>
-    <row r="905" ht="15.75" customHeight="1" s="15"/>
-    <row r="906" ht="15.75" customHeight="1" s="15"/>
-    <row r="907" ht="15.75" customHeight="1" s="15"/>
-    <row r="908" ht="15.75" customHeight="1" s="15"/>
-    <row r="909" ht="15.75" customHeight="1" s="15"/>
-    <row r="910" ht="15.75" customHeight="1" s="15"/>
-    <row r="911" ht="15.75" customHeight="1" s="15"/>
-    <row r="912" ht="15.75" customHeight="1" s="15"/>
-    <row r="913" ht="15.75" customHeight="1" s="15"/>
-    <row r="914" ht="15.75" customHeight="1" s="15"/>
-    <row r="915" ht="15.75" customHeight="1" s="15"/>
-    <row r="916" ht="15.75" customHeight="1" s="15"/>
-    <row r="917" ht="15.75" customHeight="1" s="15"/>
-    <row r="918" ht="15.75" customHeight="1" s="15"/>
-    <row r="919" ht="15.75" customHeight="1" s="15"/>
-    <row r="920" ht="15.75" customHeight="1" s="15"/>
-    <row r="921" ht="15.75" customHeight="1" s="15"/>
-    <row r="922" ht="15.75" customHeight="1" s="15"/>
-    <row r="923" ht="15.75" customHeight="1" s="15"/>
-    <row r="924" ht="15.75" customHeight="1" s="15"/>
-    <row r="925" ht="15.75" customHeight="1" s="15"/>
-    <row r="926" ht="15.75" customHeight="1" s="15"/>
-    <row r="927" ht="15.75" customHeight="1" s="15"/>
-    <row r="928" ht="15.75" customHeight="1" s="15"/>
-    <row r="929" ht="15.75" customHeight="1" s="15"/>
-    <row r="930" ht="15.75" customHeight="1" s="15"/>
-    <row r="931" ht="15.75" customHeight="1" s="15"/>
-    <row r="932" ht="15.75" customHeight="1" s="15"/>
-    <row r="933" ht="15.75" customHeight="1" s="15"/>
-    <row r="934" ht="15.75" customHeight="1" s="15"/>
-    <row r="935" ht="15.75" customHeight="1" s="15"/>
-    <row r="936" ht="15.75" customHeight="1" s="15"/>
-    <row r="937" ht="15.75" customHeight="1" s="15"/>
-    <row r="938" ht="15.75" customHeight="1" s="15"/>
-    <row r="939" ht="15.75" customHeight="1" s="15"/>
-    <row r="940" ht="15.75" customHeight="1" s="15"/>
-    <row r="941" ht="15.75" customHeight="1" s="15"/>
-    <row r="942" ht="15.75" customHeight="1" s="15"/>
-    <row r="943" ht="15.75" customHeight="1" s="15"/>
-    <row r="944" ht="15.75" customHeight="1" s="15"/>
-    <row r="945" ht="15.75" customHeight="1" s="15"/>
-    <row r="946" ht="15.75" customHeight="1" s="15"/>
-    <row r="947" ht="15.75" customHeight="1" s="15"/>
-    <row r="948" ht="15.75" customHeight="1" s="15"/>
-    <row r="949" ht="15.75" customHeight="1" s="15"/>
-    <row r="950" ht="15.75" customHeight="1" s="15"/>
-    <row r="951" ht="15.75" customHeight="1" s="15"/>
-    <row r="952" ht="15.75" customHeight="1" s="15"/>
-    <row r="953" ht="15.75" customHeight="1" s="15"/>
-    <row r="954" ht="15.75" customHeight="1" s="15"/>
-    <row r="955" ht="15.75" customHeight="1" s="15"/>
-    <row r="956" ht="15.75" customHeight="1" s="15"/>
-    <row r="957" ht="15.75" customHeight="1" s="15"/>
-    <row r="958" ht="15.75" customHeight="1" s="15"/>
-    <row r="959" ht="15.75" customHeight="1" s="15"/>
-    <row r="960" ht="15.75" customHeight="1" s="15"/>
-    <row r="961" ht="15.75" customHeight="1" s="15"/>
-    <row r="962" ht="15.75" customHeight="1" s="15"/>
-    <row r="963" ht="15.75" customHeight="1" s="15"/>
-    <row r="964" ht="15.75" customHeight="1" s="15"/>
-    <row r="965" ht="15.75" customHeight="1" s="15"/>
-    <row r="966" ht="15.75" customHeight="1" s="15"/>
-    <row r="967" ht="15.75" customHeight="1" s="15"/>
-    <row r="968" ht="15.75" customHeight="1" s="15"/>
-    <row r="969" ht="15.75" customHeight="1" s="15"/>
-    <row r="970" ht="15.75" customHeight="1" s="15"/>
-    <row r="971" ht="15.75" customHeight="1" s="15"/>
-    <row r="972" ht="15.75" customHeight="1" s="15"/>
-    <row r="973" ht="15.75" customHeight="1" s="15"/>
-    <row r="974" ht="15.75" customHeight="1" s="15"/>
-    <row r="975" ht="15.75" customHeight="1" s="15"/>
-    <row r="976" ht="15.75" customHeight="1" s="15"/>
-    <row r="977" ht="15.75" customHeight="1" s="15"/>
-    <row r="978" ht="15.75" customHeight="1" s="15"/>
-    <row r="979" ht="15.75" customHeight="1" s="15"/>
-    <row r="980" ht="15.75" customHeight="1" s="15"/>
-    <row r="981" ht="15.75" customHeight="1" s="15"/>
-    <row r="982" ht="15.75" customHeight="1" s="15"/>
-    <row r="983" ht="15.75" customHeight="1" s="15"/>
-    <row r="984" ht="15.75" customHeight="1" s="15"/>
-    <row r="985" ht="15.75" customHeight="1" s="15"/>
-    <row r="986" ht="15.75" customHeight="1" s="15"/>
-    <row r="987" ht="15.75" customHeight="1" s="15"/>
-    <row r="988" ht="15.75" customHeight="1" s="15"/>
-    <row r="989" ht="15.75" customHeight="1" s="15"/>
-    <row r="990" ht="15.75" customHeight="1" s="15"/>
-    <row r="991" ht="15.75" customHeight="1" s="15"/>
-    <row r="992" ht="15.75" customHeight="1" s="15"/>
-    <row r="993" ht="15.75" customHeight="1" s="15"/>
-    <row r="994" ht="15.75" customHeight="1" s="15"/>
-    <row r="995" ht="15.75" customHeight="1" s="15"/>
-    <row r="996" ht="15.75" customHeight="1" s="15"/>
-    <row r="997" ht="15.75" customHeight="1" s="15"/>
-    <row r="998" ht="15.75" customHeight="1" s="15"/>
-    <row r="999" ht="15.75" customHeight="1" s="15"/>
-    <row r="1000" ht="15.75" customHeight="1" s="15"/>
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="108" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="109" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="110" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="111" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="112" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="113" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="114" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="115" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="116" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="117" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="118" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="119" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="120" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="121" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="122" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="123" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="124" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="125" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="126" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="127" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="128" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="129" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="130" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="131" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="132" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="133" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="134" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="135" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="136" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="137" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="138" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="139" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="140" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="141" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="142" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="143" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="144" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="145" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="146" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="147" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="148" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="149" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="150" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="151" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="152" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="153" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="154" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="155" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="156" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="157" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="158" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="159" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="160" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="161" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="162" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="163" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="164" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="165" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="166" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="167" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="168" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="169" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="170" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="171" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="172" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="173" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="174" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="175" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="176" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="177" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="178" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="179" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="180" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="181" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="182" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="183" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="184" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="185" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="186" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="187" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="188" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="189" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="190" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="191" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="192" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="193" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="194" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="195" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="196" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="197" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="198" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="199" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="200" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="201" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="202" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="203" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="204" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="205" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="206" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="207" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="208" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="209" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="210" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="211" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="212" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="213" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="214" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="215" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="216" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="217" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="218" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="219" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="220" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="221" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="222" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="223" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="224" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="225" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="226" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="227" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="228" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="229" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="230" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="231" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="232" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="233" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="234" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="235" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="236" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="237" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="238" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="239" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="240" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="241" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="242" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="243" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="244" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="245" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="246" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="247" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="248" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="249" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="250" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="251" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="252" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="253" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="254" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="255" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="256" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="257" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="258" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="259" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="260" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="261" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="262" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="263" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="264" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="265" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="266" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="267" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="268" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="269" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="270" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="271" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="272" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="273" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="274" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="275" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="276" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="277" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="278" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="279" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="280" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="281" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="282" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="283" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="284" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="285" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="286" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="287" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="288" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="289" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="290" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="291" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="292" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="293" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="294" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="295" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="296" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="297" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="298" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="299" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="300" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="301" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="302" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="303" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="304" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="305" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="306" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="307" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="308" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="309" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="310" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="311" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="312" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="313" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="314" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="315" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="316" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="317" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="318" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="319" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="320" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="321" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="322" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="323" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="324" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="325" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="326" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="327" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="328" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="329" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="330" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="331" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="332" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="333" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="334" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="335" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="336" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="337" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="338" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="339" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="340" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="341" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="342" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="343" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="344" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="345" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="346" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="347" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="348" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="349" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="350" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="351" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="352" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="353" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="354" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="355" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="356" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="357" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="358" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="359" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="360" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="361" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="362" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="363" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="364" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="365" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="366" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="367" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="368" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="369" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="370" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="371" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="372" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="373" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="374" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="375" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="376" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="377" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="378" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="379" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="380" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="381" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="382" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="383" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="384" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="385" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="386" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="387" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="388" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="389" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="390" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="391" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="392" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="393" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="394" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="395" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="396" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="397" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="398" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="399" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="400" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="401" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="402" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="403" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="404" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="405" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="406" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="407" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="408" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="409" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="410" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="411" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="412" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="413" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="414" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="415" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="416" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="417" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="418" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="419" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="420" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="421" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="422" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="423" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="424" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="425" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="426" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="427" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="428" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="429" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="430" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="431" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="432" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="433" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="434" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="435" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="436" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="437" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="438" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="439" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="440" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="441" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="442" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="443" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="444" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="445" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="446" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="447" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="448" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="449" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="450" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="451" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="452" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="453" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="454" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="455" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="456" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="457" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="458" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="459" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="460" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="461" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="462" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="463" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="464" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="465" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="466" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="467" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="468" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="469" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="470" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="471" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="472" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="473" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="474" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="475" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="476" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="477" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="478" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="479" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="480" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="481" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="482" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="483" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="484" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="485" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="486" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="487" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="488" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="489" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="490" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="491" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="492" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="493" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="494" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="495" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="496" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="497" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="498" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="499" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="500" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="501" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="502" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="503" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="504" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="505" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="506" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="507" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="508" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="509" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="510" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="511" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="512" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="513" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="514" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="515" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="516" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="517" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="518" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="519" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="520" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="521" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="522" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="523" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="524" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="525" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="526" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="527" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="528" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="529" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="530" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="531" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="532" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="533" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="534" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="535" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="536" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="537" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="538" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="539" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="540" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="541" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="542" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="543" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="544" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="545" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="546" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="547" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="548" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="549" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="550" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="551" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="552" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="553" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="554" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="555" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="556" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="557" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="558" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="559" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="560" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="561" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="562" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="563" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="564" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="565" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="566" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="567" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="568" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="569" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="570" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="571" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="572" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="573" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="574" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="575" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="576" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="577" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="578" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="579" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="580" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="581" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="582" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="583" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="584" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="585" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="586" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="587" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="588" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="589" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="590" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="591" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="592" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="593" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="594" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="595" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="596" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="597" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="598" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="599" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="600" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="601" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="602" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="603" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="604" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="605" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="606" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="607" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="608" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="609" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="610" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="611" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="612" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="613" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="614" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="615" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="616" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="617" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="618" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="619" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="620" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="621" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="622" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="623" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="624" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="625" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="626" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="627" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="628" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="629" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="630" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="631" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="632" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="633" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="634" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="635" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="636" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="637" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="638" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="639" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="640" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="641" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="642" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="643" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="644" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="645" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="646" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="647" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="648" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="649" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="650" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="651" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="652" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="653" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="654" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="655" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="656" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="657" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="658" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="659" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="660" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="661" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="662" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="663" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="664" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="665" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="666" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="667" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="668" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="669" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="670" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="671" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="672" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="673" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="674" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="675" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="676" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="677" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="678" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="679" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="680" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="681" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="682" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="683" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="684" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="685" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="686" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="687" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="688" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="689" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="690" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="691" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="692" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="693" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="694" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="695" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="696" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="697" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="698" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="699" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="700" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="701" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="702" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="703" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="704" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="705" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="706" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="707" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="708" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="709" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="710" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="711" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="712" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="713" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="714" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="715" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="716" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="717" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="718" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="719" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="720" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="721" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="722" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="723" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="724" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="725" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="726" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="727" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="728" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="729" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="730" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="731" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="732" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="733" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="734" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="735" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="736" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="737" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="738" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="739" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="740" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="741" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="742" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="743" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="744" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="745" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="746" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="747" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="748" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="749" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="750" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="751" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="752" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="753" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="754" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="755" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="756" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="757" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="758" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="759" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="760" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="761" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="762" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="763" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="764" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="765" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="766" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="767" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="768" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="769" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="770" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="771" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="772" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="773" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="774" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="775" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="776" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="777" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="778" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="779" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="780" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="781" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="782" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="783" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="784" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="785" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="786" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="787" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="788" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="789" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="790" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="791" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="792" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="793" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="794" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="795" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="796" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="797" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="798" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="799" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="800" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="801" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="802" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="803" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="804" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="805" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="806" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="807" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="808" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="809" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="810" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="811" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="812" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="813" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="814" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="815" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="816" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="817" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="818" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="819" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="820" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="821" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="822" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="823" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="824" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="825" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="826" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="827" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="828" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="829" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="830" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="831" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="832" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="833" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="834" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="835" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="836" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="837" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="838" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="839" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="840" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="841" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="842" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="843" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="844" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="845" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="846" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="847" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="848" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="849" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="850" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="851" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="852" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="853" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="854" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="855" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="856" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="857" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="858" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="859" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="860" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="861" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="862" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="863" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="864" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="865" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="866" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="867" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="868" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="869" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="870" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="871" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="872" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="873" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="874" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="875" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="876" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="877" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="878" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="879" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="880" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="881" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="882" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="883" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="884" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="885" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="886" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="887" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="888" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="889" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="890" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="891" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="892" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="893" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="894" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="895" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="896" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="897" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="898" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="899" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="900" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="901" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="902" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="903" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="904" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="905" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="906" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="907" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="908" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="909" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="910" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="911" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="912" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="913" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="914" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="915" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="916" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="917" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="918" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="919" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="920" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="921" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="922" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="923" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="924" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="925" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="926" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="927" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="928" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="929" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="930" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="931" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="932" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="933" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="934" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="935" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="936" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="937" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="938" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="939" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="940" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="941" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="942" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="943" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="944" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="945" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="946" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="947" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="948" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="949" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="950" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="951" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="952" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="953" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="954" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="955" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="956" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="957" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="958" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="959" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="960" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="961" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="962" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="963" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="964" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="965" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="966" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="967" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="968" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="969" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="970" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="971" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="972" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="973" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="974" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="975" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="976" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="977" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="978" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="979" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="980" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="981" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="982" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="983" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="984" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="985" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="986" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="987" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="988" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="989" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="990" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="991" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="992" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="993" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="994" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="995" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="996" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="997" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="998" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="999" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1000" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:T2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId11"/>
+    <hyperlink ref="A6" r:id="rId1" display="CityUoL__qwen3.5-2b__Qwen-GuidePlay-2B-v1"/>
+    <hyperlink ref="A7" r:id="rId2" display="DAIR__qwen3.5-2b__sft-dpo-v2"/>
+    <hyperlink ref="A8" r:id="rId3" display="DAIR__qwen3.5-2b__sft-v1"/>
+    <hyperlink ref="A9" r:id="rId4" display="playornotplay__qwen3.5-2b__playornotplay-v1.0-merged-fp32-828e356"/>
+    <hyperlink ref="A11" r:id="rId5" display="Bentel rockers__qwen3.5-4b__Bentel_iter"/>
+    <hyperlink ref="A12" r:id="rId6" display="Bentel rockers__qwen3.5-4b__Bentel_iter_2"/>
+    <hyperlink ref="A13" r:id="rId7" display="Bentel rockers__qwen3.5-4b__Bentel_iter_3"/>
+    <hyperlink ref="A16" r:id="rId8" display="BSU-SLIM__Qwen3.5-9B-Base__playpen-prm-9b-best_of_n"/>
+    <hyperlink ref="A17" r:id="rId9" display="Dialogue Architects__qwen3.5-9b__SCoRe_Qwen3.5-9B"/>
+    <hyperlink ref="A18" r:id="rId10" display="LLP: Large Language Problems__qwen3.5-9b__llp-final"/>
+    <hyperlink ref="A20" r:id="rId11" display="SLED-BSU__Qwen3.5-27B-sft-ep1__prm-ep1-best_of_n"/>
   </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/summaries/summary_report.xlsx
+++ b/summaries/summary_report.xlsx
@@ -1034,7 +1034,7 @@
         <v>10.67</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>44.24</v>
+        <v>46.41</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>6.7</v>
@@ -1055,13 +1055,13 @@
         <v>10.56</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>40.2</v>
+        <v>41.92</v>
       </c>
       <c r="M5" s="6" t="n">
         <v>99.40000000000001</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>40.44</v>
+        <v>42.17</v>
       </c>
       <c r="O5" s="6" t="n">
         <v>0</v>
@@ -1241,7 +1241,7 @@
         <v>100</v>
       </c>
       <c r="BV5" s="6" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="BW5" s="6" t="n">
         <v>100</v>
@@ -1288,7 +1288,7 @@
         <v>35.99</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>-1.94</v>
+        <v>-4.11</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>40.62</v>
@@ -1309,13 +1309,13 @@
         <v>11.22</v>
       </c>
       <c r="L6" s="10" t="n">
-        <v>-0.34</v>
+        <v>-2.06</v>
       </c>
       <c r="M6" s="10" t="n">
         <v>-1.6</v>
       </c>
-      <c r="N6" s="9" t="n">
-        <v>0.32</v>
+      <c r="N6" s="10" t="n">
+        <v>-1.41</v>
       </c>
       <c r="O6" s="9" t="n">
         <v>10</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="BV6" s="9" t="n">
-        <v>34.62</v>
+        <v>25.97</v>
       </c>
       <c r="BW6" s="11" t="n">
         <v>0</v>
@@ -1542,7 +1542,7 @@
         <v>38.93</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>-0.71</v>
+        <v>-2.88</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>46.42</v>
@@ -1563,13 +1563,13 @@
         <v>15.11</v>
       </c>
       <c r="L7" s="10" t="n">
-        <v>-0.68</v>
+        <v>-2.4</v>
       </c>
       <c r="M7" s="9" t="n">
         <v>0.6</v>
       </c>
       <c r="N7" s="10" t="n">
-        <v>-0.92</v>
+        <v>-2.65</v>
       </c>
       <c r="O7" s="9" t="n">
         <v>60</v>
@@ -1749,7 +1749,7 @@
         <v>0</v>
       </c>
       <c r="BV7" s="9" t="n">
-        <v>10.58</v>
+        <v>1.93</v>
       </c>
       <c r="BW7" s="11" t="n">
         <v>0</v>
@@ -1795,8 +1795,8 @@
       <c r="D8" s="9" t="n">
         <v>35.34</v>
       </c>
-      <c r="E8" s="9" t="n">
-        <v>0.11</v>
+      <c r="E8" s="10" t="n">
+        <v>-2.06</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>41.54</v>
@@ -1817,13 +1817,13 @@
         <v>18.18</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>-2.83</v>
+        <v>-4.55</v>
       </c>
       <c r="M8" s="9" t="n">
         <v>0.4</v>
       </c>
       <c r="N8" s="10" t="n">
-        <v>-3</v>
+        <v>-4.73</v>
       </c>
       <c r="O8" s="9" t="n">
         <v>50</v>
@@ -2002,8 +2002,8 @@
       <c r="BU8" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="BV8" s="9" t="n">
-        <v>5.77</v>
+      <c r="BV8" s="10" t="n">
+        <v>-2.88</v>
       </c>
       <c r="BW8" s="11" t="n">
         <v>0</v>
@@ -2050,7 +2050,7 @@
         <v>28.25</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>-0.1</v>
+        <v>-2.27</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>33.54</v>
@@ -2071,13 +2071,13 @@
         <v>13.25</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>2.73</v>
+        <v>1.01</v>
       </c>
       <c r="M9" s="10" t="n">
         <v>-1.6</v>
       </c>
       <c r="N9" s="9" t="n">
-        <v>3.46</v>
+        <v>1.73</v>
       </c>
       <c r="O9" s="9" t="n">
         <v>100</v>
@@ -2257,7 +2257,7 @@
         <v>0</v>
       </c>
       <c r="BV9" s="9" t="n">
-        <v>39.42</v>
+        <v>30.77</v>
       </c>
       <c r="BW9" s="11" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>26.66</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>51.33</v>
+        <v>55.08</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>29.28</v>
@@ -2317,13 +2317,13 @@
         <v>39.52</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>48.74</v>
+        <v>53.53</v>
       </c>
       <c r="M10" s="6" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>48.94</v>
+        <v>53.74</v>
       </c>
       <c r="O10" s="6" t="n">
         <v>57.5</v>
@@ -2503,7 +2503,7 @@
         <v>100</v>
       </c>
       <c r="BV10" s="6" t="n">
-        <v>0</v>
+        <v>24.04</v>
       </c>
       <c r="BW10" s="6" t="n">
         <v>100</v>
@@ -2549,8 +2549,8 @@
       <c r="D11" s="9" t="n">
         <v>4.92</v>
       </c>
-      <c r="E11" s="9" t="n">
-        <v>2.94</v>
+      <c r="E11" s="10" t="n">
+        <v>-0.8100000000000001</v>
       </c>
       <c r="F11" s="9" t="n">
         <v>4.02</v>
@@ -2570,14 +2570,14 @@
       <c r="K11" s="10" t="n">
         <v>-4.2</v>
       </c>
-      <c r="L11" s="9" t="n">
-        <v>1.58</v>
+      <c r="L11" s="10" t="n">
+        <v>-3.21</v>
       </c>
       <c r="M11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N11" s="9" t="n">
-        <v>1.58</v>
+      <c r="N11" s="10" t="n">
+        <v>-3.22</v>
       </c>
       <c r="O11" s="9" t="n">
         <v>17.5</v>
@@ -2756,8 +2756,8 @@
       <c r="BU11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="BV11" s="9" t="n">
-        <v>20.19</v>
+      <c r="BV11" s="10" t="n">
+        <v>-3.85</v>
       </c>
       <c r="BW11" s="11" t="n">
         <v>0</v>
@@ -2804,7 +2804,7 @@
         <v>-2.39</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>-3.96</v>
+        <v>-7.71</v>
       </c>
       <c r="F12" s="10" t="n">
         <v>-0.8100000000000001</v>
@@ -2825,13 +2825,13 @@
         <v>-20.94</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>-5.1</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="M12" s="9" t="n">
         <v>0.2</v>
       </c>
       <c r="N12" s="10" t="n">
-        <v>-5.21</v>
+        <v>-10.01</v>
       </c>
       <c r="O12" s="9" t="n">
         <v>7.5</v>
@@ -3011,7 +3011,7 @@
         <v>0</v>
       </c>
       <c r="BV12" s="9" t="n">
-        <v>30.77</v>
+        <v>6.73</v>
       </c>
       <c r="BW12" s="11" t="n">
         <v>0</v>
@@ -3057,8 +3057,8 @@
       <c r="D13" s="9" t="n">
         <v>6.69</v>
       </c>
-      <c r="E13" s="9" t="n">
-        <v>2.94</v>
+      <c r="E13" s="10" t="n">
+        <v>-0.8100000000000001</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>4.46</v>
@@ -3078,14 +3078,14 @@
       <c r="K13" s="10" t="n">
         <v>-4.2</v>
       </c>
-      <c r="L13" s="9" t="n">
-        <v>1.58</v>
+      <c r="L13" s="10" t="n">
+        <v>-3.21</v>
       </c>
       <c r="M13" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N13" s="9" t="n">
-        <v>1.58</v>
+      <c r="N13" s="10" t="n">
+        <v>-3.22</v>
       </c>
       <c r="O13" s="9" t="n">
         <v>22.5</v>
@@ -3264,8 +3264,8 @@
       <c r="BU13" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="BV13" s="9" t="n">
-        <v>20.19</v>
+      <c r="BV13" s="10" t="n">
+        <v>-3.85</v>
       </c>
       <c r="BW13" s="11" t="n">
         <v>0</v>
@@ -3550,7 +3550,7 @@
         <v>31.91</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>53.9</v>
+        <v>57.49</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>37.37</v>
@@ -3571,13 +3571,13 @@
         <v>45.07</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>50.2</v>
+        <v>53.85</v>
       </c>
       <c r="M15" s="6" t="n">
         <v>100</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>50.2</v>
+        <v>53.85</v>
       </c>
       <c r="O15" s="6" t="n">
         <v>87.5</v>
@@ -3757,7 +3757,7 @@
         <v>100</v>
       </c>
       <c r="BV15" s="6" t="n">
-        <v>0</v>
+        <v>18.27</v>
       </c>
       <c r="BW15" s="6" t="n">
         <v>100</v>
@@ -3804,7 +3804,7 @@
         <v>4.7</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>-3.98</v>
+        <v>-7.57</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>0.17</v>
@@ -3825,13 +3825,13 @@
         <v>-19.55</v>
       </c>
       <c r="L16" s="10" t="n">
-        <v>-3.44</v>
+        <v>-7.09</v>
       </c>
       <c r="M16" s="10" t="n">
         <v>-0.4</v>
       </c>
       <c r="N16" s="10" t="n">
-        <v>-3.25</v>
+        <v>-6.9</v>
       </c>
       <c r="O16" s="10" t="n">
         <v>-42.5</v>
@@ -4010,8 +4010,8 @@
       <c r="BU16" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="BV16" s="9" t="n">
-        <v>1.92</v>
+      <c r="BV16" s="10" t="n">
+        <v>-16.35</v>
       </c>
       <c r="BW16" s="11" t="n">
         <v>0</v>
@@ -4078,14 +4078,14 @@
       <c r="K17" s="10" t="n">
         <v>-0.87</v>
       </c>
-      <c r="L17" s="10" t="n">
-        <v>-0.1</v>
+      <c r="L17" s="9" t="n">
+        <v>0.48</v>
       </c>
       <c r="M17" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="N17" s="10" t="n">
-        <v>-0.1</v>
+      <c r="N17" s="9" t="n">
+        <v>0.48</v>
       </c>
       <c r="O17" s="10" t="n">
         <v>-10</v>
@@ -4264,8 +4264,8 @@
       <c r="BU17" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="BV17" s="11" t="n">
-        <v>0</v>
+      <c r="BV17" s="9" t="n">
+        <v>2.88</v>
       </c>
       <c r="BW17" s="11" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
         <v>21.48</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>3.9</v>
+        <v>0.31</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>22.82</v>
@@ -4333,13 +4333,13 @@
         <v>-8.1</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>4.29</v>
+        <v>0.64</v>
       </c>
       <c r="M18" s="10" t="n">
         <v>-0.4</v>
       </c>
       <c r="N18" s="9" t="n">
-        <v>4.51</v>
+        <v>0.86</v>
       </c>
       <c r="O18" s="9" t="n">
         <v>12.5</v>
@@ -4519,7 +4519,7 @@
         <v>0</v>
       </c>
       <c r="BV18" s="9" t="n">
-        <v>33.65</v>
+        <v>15.38</v>
       </c>
       <c r="BW18" s="11" t="n">
         <v>0</v>
